--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45370</v>
+        <v>46077</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,19 +1859,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,46 +1899,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1948,14 +1944,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46077</v>
+        <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1967,8 +1963,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1977,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1995,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2008,42 +2009,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2053,14 +2054,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44986</v>
+        <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,21 +2075,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2102,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2114,46 +2115,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2167,10 +2168,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45244</v>
+        <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,23 +2183,18 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2212,7 +2208,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2224,50 +2220,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2277,14 +2269,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45979</v>
+        <v>44986</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2298,20 +2290,20 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2326,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2338,46 +2330,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2383,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44889</v>
+        <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,16 +2398,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2452,42 +2439,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2501,10 +2492,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,17 +2507,22 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2541,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2553,39 +2549,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3286,7 +3286,7 @@
         <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3357,14 +3357,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45537</v>
+        <v>45007</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,11 +3378,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44937</v>
+        <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44599</v>
+        <v>45527</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3527,13 +3527,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3576,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3590,10 +3585,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44916</v>
+        <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3605,13 +3600,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3654,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3668,10 +3658,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45007</v>
+        <v>46041</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3683,13 +3673,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3732,7 +3717,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3746,10 +3731,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45027</v>
+        <v>46041</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3761,13 +3746,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3810,7 +3790,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3824,10 +3804,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45344</v>
+        <v>45933</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3840,7 +3820,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3900,7 +3880,7 @@
         <v>46077</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3956,7 +3936,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3970,10 +3950,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44599</v>
+        <v>46079</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3986,7 +3966,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4029,7 +4009,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4046,7 +4026,7 @@
         <v>46079</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4059,7 +4039,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4102,7 +4082,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4112,14 +4092,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
         <v>46079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4132,7 +4112,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4175,7 +4155,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4192,7 +4172,7 @@
         <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4205,7 +4185,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4248,7 +4228,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4258,14 +4238,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4278,7 +4258,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4321,7 +4301,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4335,10 +4315,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45933</v>
+        <v>44840</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4351,7 +4331,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4394,7 +4374,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4408,10 +4388,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46090</v>
+        <v>45019</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4423,8 +4403,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4467,7 +4452,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4481,10 +4466,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45968</v>
+        <v>45379</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4496,13 +4481,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4545,7 +4525,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4559,10 +4539,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45968</v>
+        <v>44680</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4574,13 +4554,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>7.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4623,7 +4598,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4637,10 +4612,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45007</v>
+        <v>45968</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4658,7 +4633,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4701,7 +4676,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4715,10 +4690,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45979</v>
+        <v>45968</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4732,11 +4707,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4779,7 +4754,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4796,7 +4771,7 @@
         <v>45979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4814,7 +4789,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4857,7 +4832,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4874,7 +4849,7 @@
         <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4892,7 +4867,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4935,7 +4910,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4949,10 +4924,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45988</v>
+        <v>46139</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4964,13 +4939,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5013,7 +4983,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5027,10 +4997,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45835</v>
+        <v>45979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5042,8 +5012,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5086,7 +5061,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5100,10 +5075,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45832</v>
+        <v>45988</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5115,8 +5090,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5159,7 +5139,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5173,10 +5153,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44916</v>
+        <v>45835</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5188,13 +5168,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5237,7 +5212,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5251,10 +5226,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45379</v>
+        <v>45832</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5267,7 +5242,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5310,7 +5285,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5324,10 +5299,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45373</v>
+        <v>46079</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5340,7 +5315,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5383,7 +5358,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5393,14 +5368,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46041</v>
+        <v>45537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5412,8 +5387,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5456,7 +5436,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5466,14 +5446,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46041</v>
+        <v>45537</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5485,8 +5465,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5529,7 +5514,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5543,10 +5528,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45553</v>
+        <v>45373</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5558,8 +5543,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5592,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5616,10 +5606,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46139</v>
+        <v>44756</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5632,7 +5622,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5675,7 +5665,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5685,14 +5675,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45736</v>
+        <v>45527</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5705,7 +5695,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5748,7 +5738,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5762,10 +5752,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46079</v>
+        <v>46273</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5778,7 +5768,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5811,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5825,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44840</v>
+        <v>44916</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,8 +5840,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5889,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5908,10 +5903,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45280</v>
+        <v>45007</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5923,8 +5918,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5967,7 +5967,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44840</v>
+        <v>44599</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5996,8 +5996,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6040,7 +6045,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6054,10 +6059,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44680</v>
+        <v>44916</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6069,8 +6074,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6113,7 +6123,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6127,10 +6137,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45016</v>
+        <v>45553</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6142,13 +6152,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6191,7 +6196,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6201,14 +6206,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45537</v>
+        <v>44937</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6220,13 +6225,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45007</v>
+        <v>45344</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6298,13 +6298,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6347,7 +6342,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6361,10 +6356,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45373</v>
+        <v>45370</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6376,13 +6371,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6425,7 +6415,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6439,10 +6429,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45373</v>
+        <v>45027</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6456,11 +6446,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6503,7 +6493,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6517,10 +6507,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44937</v>
+        <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6532,8 +6522,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6576,7 +6571,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6590,10 +6585,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45019</v>
+        <v>45373</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6605,13 +6600,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6654,7 +6644,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6668,10 +6658,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45537</v>
+        <v>45736</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6683,13 +6673,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6732,7 +6717,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6746,10 +6731,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45370</v>
+        <v>45280</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6762,7 +6747,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>9.5</v>
+        <v>2.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6805,7 +6790,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6819,10 +6804,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44756</v>
+        <v>45016</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6834,8 +6819,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6868,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6888,14 +6878,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46273</v>
+        <v>45537</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6907,8 +6897,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6946,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6960,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45527</v>
+        <v>45007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6980,8 +6975,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45593</v>
+        <v>44937</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7107,14 +7107,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45527</v>
+        <v>45593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46077</v>
+        <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,19 +1859,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,42 +1899,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1948,10 +1952,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45979</v>
+        <v>44889</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1965,11 +1969,11 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2009,42 +2013,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2054,14 +2058,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44889</v>
+        <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2075,20 +2079,20 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>9.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2103,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2115,46 +2119,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2168,10 +2172,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46220</v>
+        <v>45979</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2183,8 +2187,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2224,42 +2233,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2269,14 +2278,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44986</v>
+        <v>45244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2290,11 +2299,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2334,42 +2343,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2379,14 +2392,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45370</v>
+        <v>46077</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2399,19 +2412,19 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2426,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2439,46 +2452,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2492,10 +2501,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45244</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2507,23 +2516,18 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2537,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2549,43 +2553,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45537</v>
+        <v>44840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3298,13 +3298,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3342,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3361,10 +3356,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45007</v>
+        <v>45280</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3376,13 +3371,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3415,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3435,14 +3425,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44599</v>
+        <v>46079</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3455,7 +3445,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3488,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3502,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45527</v>
+        <v>46079</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3528,7 +3518,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3571,7 +3561,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3581,14 +3571,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44840</v>
+        <v>46079</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3601,7 +3591,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3634,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3654,14 +3644,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46041</v>
+        <v>46079</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3674,7 +3664,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3717,7 +3707,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3727,14 +3717,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46041</v>
+        <v>45537</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3746,8 +3736,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3790,7 +3785,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3800,14 +3795,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45933</v>
+        <v>45537</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3819,8 +3814,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3873,14 +3873,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46077</v>
+        <v>46090</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>5.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3950,10 +3950,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46079</v>
+        <v>44937</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4009,7 +4009,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4019,14 +4019,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46079</v>
+        <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4038,8 +4038,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4082,7 +4087,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4092,14 +4097,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46079</v>
+        <v>44916</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4111,8 +4116,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4155,7 +4165,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4165,14 +4175,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46079</v>
+        <v>45007</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4184,8 +4194,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4228,7 +4243,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4242,10 +4257,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46090</v>
+        <v>45027</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4257,8 +4272,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4301,7 +4321,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4315,10 +4335,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44840</v>
+        <v>45933</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4331,7 +4351,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4374,7 +4394,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4388,10 +4408,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45019</v>
+        <v>45835</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4403,13 +4423,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4452,7 +4467,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4466,10 +4481,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45379</v>
+        <v>45832</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4482,7 +4497,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4525,7 +4540,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4539,10 +4554,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44680</v>
+        <v>45344</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4555,7 +4570,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4598,7 +4613,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4615,7 +4630,7 @@
         <v>45968</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4633,7 +4648,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4676,7 +4691,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4690,10 +4705,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45968</v>
+        <v>44599</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4705,13 +4720,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>3.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4754,7 +4764,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4768,10 +4778,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45979</v>
+        <v>45968</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4785,11 +4795,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4832,7 +4842,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4849,7 +4859,7 @@
         <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4867,7 +4877,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4910,7 +4920,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4924,10 +4934,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46139</v>
+        <v>44840</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4940,7 +4950,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4983,7 +4993,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5000,7 +5010,7 @@
         <v>45979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5018,7 +5028,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5061,7 +5071,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5075,10 +5085,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45988</v>
+        <v>45979</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5092,11 +5102,11 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5139,7 +5149,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5153,10 +5163,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45835</v>
+        <v>46139</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5169,7 +5179,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5212,7 +5222,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5226,10 +5236,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45832</v>
+        <v>44680</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5242,7 +5252,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>7.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5285,7 +5295,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5299,10 +5309,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46079</v>
+        <v>45988</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5314,8 +5324,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5358,7 +5373,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5368,14 +5383,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45537</v>
+        <v>45007</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5389,11 +5404,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5436,7 +5451,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5446,14 +5461,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45537</v>
+        <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5465,13 +5480,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5514,7 +5524,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5528,10 +5538,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45373</v>
+        <v>46041</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5543,13 +5553,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5592,7 +5597,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5606,10 +5611,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44756</v>
+        <v>46041</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5622,7 +5627,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5665,7 +5670,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5679,10 +5684,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45527</v>
+        <v>44916</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5694,8 +5699,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5738,7 +5748,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5752,10 +5762,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46273</v>
+        <v>45379</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5768,7 +5778,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5811,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5825,10 +5835,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44916</v>
+        <v>45373</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5840,13 +5850,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5889,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5899,14 +5904,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45007</v>
+        <v>46077</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5918,13 +5923,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5967,7 +5967,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5981,10 +5981,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44599</v>
+        <v>45016</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6045,7 +6045,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6055,14 +6055,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44916</v>
+        <v>45537</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45553</v>
+        <v>45007</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6152,8 +6152,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6196,7 +6201,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6210,10 +6215,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44937</v>
+        <v>45373</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6225,8 +6230,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6269,7 +6279,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6283,10 +6293,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45344</v>
+        <v>45373</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6298,8 +6308,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>0.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6342,7 +6357,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6356,10 +6371,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45370</v>
+        <v>44937</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6372,7 +6387,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>9.5</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6415,7 +6430,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6429,10 +6444,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45027</v>
+        <v>45553</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6444,13 +6459,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6493,7 +6503,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6503,14 +6513,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45373</v>
+        <v>45736</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6522,13 +6532,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6571,7 +6576,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6585,10 +6590,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45373</v>
+        <v>45019</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6600,8 +6605,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6644,7 +6654,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6658,10 +6668,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45736</v>
+        <v>45537</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6673,8 +6683,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6717,7 +6732,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6731,10 +6746,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45280</v>
+        <v>45370</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6747,7 +6762,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>9.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6790,7 +6805,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6804,10 +6819,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45016</v>
+        <v>44756</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6819,13 +6834,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6868,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6878,14 +6888,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45537</v>
+        <v>46273</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6897,13 +6907,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6946,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6960,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45007</v>
+        <v>45527</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6975,13 +6980,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44937</v>
+        <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7107,14 +7107,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45593</v>
+        <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45370</v>
+        <v>45979</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,11 +1858,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1899,46 +1904,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1948,14 +1949,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44889</v>
+        <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1967,13 +1968,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1982,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2000,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2013,42 +2009,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,14 +2054,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44986</v>
+        <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,21 +2075,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2107,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2119,46 +2115,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2168,14 +2164,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45979</v>
+        <v>44986</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2189,20 +2185,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2217,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2229,46 +2225,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2282,10 +2278,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45244</v>
+        <v>45370</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2297,13 +2293,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2312,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2327,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2339,50 +2330,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2392,14 +2383,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46077</v>
+        <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2403,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2421,10 +2412,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2439,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2452,42 +2443,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2501,10 +2492,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,17 +2507,22 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2541,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2553,39 +2549,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44840</v>
+        <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3298,8 +3298,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3342,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3356,10 +3361,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45280</v>
+        <v>45007</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3371,8 +3376,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3415,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3425,14 +3435,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46079</v>
+        <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3445,7 +3455,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3488,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3502,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46079</v>
+        <v>44840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3518,7 +3528,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3561,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3571,14 +3581,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46079</v>
+        <v>45933</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3591,7 +3601,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3634,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3644,14 +3654,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46079</v>
+        <v>46041</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3664,7 +3674,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.7</v>
+        <v>6.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3707,7 +3717,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3717,14 +3727,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45537</v>
+        <v>46041</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3736,13 +3746,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3785,7 +3790,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3795,14 +3800,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45537</v>
+        <v>44840</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3814,13 +3819,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3863,7 +3863,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46090</v>
+        <v>45019</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3892,8 +3892,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3936,7 +3941,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3950,10 +3955,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44937</v>
+        <v>45379</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3966,7 +3971,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.1</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4009,7 +4014,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4023,10 +4028,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44599</v>
+        <v>44680</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4038,13 +4043,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4087,7 +4087,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4101,10 +4101,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44916</v>
+        <v>45968</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4118,11 +4118,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4165,7 +4165,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4179,10 +4179,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45007</v>
+        <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4243,7 +4243,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4257,10 +4257,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45027</v>
+        <v>45979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4274,11 +4274,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.6</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4321,7 +4321,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45933</v>
+        <v>45979</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4350,8 +4350,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4394,7 +4399,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4408,10 +4413,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45835</v>
+        <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4423,8 +4428,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4467,7 +4477,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4477,14 +4487,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45832</v>
+        <v>46077</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4497,7 +4507,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.1</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4540,7 +4550,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4554,10 +4564,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45344</v>
+        <v>46079</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4570,7 +4580,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>3.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4613,7 +4623,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4627,10 +4637,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45968</v>
+        <v>45988</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4648,7 +4658,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4691,7 +4701,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4701,14 +4711,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44599</v>
+        <v>46079</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4721,7 +4731,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4764,7 +4774,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4774,14 +4784,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45968</v>
+        <v>46079</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4793,13 +4803,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4842,7 +4847,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4852,14 +4857,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45979</v>
+        <v>46079</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4871,13 +4876,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4920,7 +4920,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4934,10 +4934,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44840</v>
+        <v>46090</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5003,14 +5003,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45979</v>
+        <v>45537</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5071,7 +5071,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5081,14 +5081,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45979</v>
+        <v>45537</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>46139</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44680</v>
+        <v>45835</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7.7</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5295,7 +5295,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5309,10 +5309,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45988</v>
+        <v>45832</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5324,13 +5324,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5373,7 +5368,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5387,10 +5382,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45007</v>
+        <v>45373</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5404,11 +5399,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5451,7 +5446,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5465,10 +5460,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46079</v>
+        <v>44756</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5481,7 +5476,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5524,7 +5519,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5538,10 +5533,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46041</v>
+        <v>45527</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5554,7 +5549,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.3</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5597,7 +5592,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5611,10 +5606,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46041</v>
+        <v>44916</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5626,8 +5621,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5670,7 +5670,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44916</v>
+        <v>45007</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5701,11 +5701,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5748,7 +5748,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45379</v>
+        <v>46079</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45373</v>
+        <v>44599</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,8 +5850,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5899,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5904,14 +5909,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46077</v>
+        <v>44916</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5923,8 +5928,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5967,7 +5977,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5981,10 +5991,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45016</v>
+        <v>45553</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5996,13 +6006,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6045,7 +6050,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6055,14 +6060,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45537</v>
+        <v>44937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6074,13 +6079,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6123,7 +6123,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45007</v>
+        <v>45344</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6152,13 +6152,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6201,7 +6196,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6215,10 +6210,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45373</v>
+        <v>45370</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6230,13 +6225,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6279,7 +6269,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6293,10 +6283,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45373</v>
+        <v>45027</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6310,11 +6300,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6357,7 +6347,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6371,10 +6361,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44937</v>
+        <v>45373</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6386,8 +6376,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6430,7 +6425,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6444,10 +6439,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45553</v>
+        <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6460,7 +6455,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6520,7 +6515,7 @@
         <v>45736</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6576,7 +6571,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6590,10 +6585,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45019</v>
+        <v>45280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6605,13 +6600,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6654,7 +6644,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6664,14 +6654,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45537</v>
+        <v>45016</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6685,11 +6675,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6732,7 +6722,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6742,14 +6732,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45370</v>
+        <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6761,8 +6751,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6805,7 +6800,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6819,10 +6814,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44756</v>
+        <v>46273</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6835,7 +6830,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6873,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6892,10 +6887,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46273</v>
+        <v>45007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6907,8 +6902,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45527</v>
+        <v>44937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7041,7 +7041,7 @@
         <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45979</v>
+        <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,16 +1858,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1904,35 +1899,39 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
@@ -1956,7 +1955,7 @@
         <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2043,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2054,14 +2053,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44889</v>
+        <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2075,20 +2074,20 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>9.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2103,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2115,46 +2114,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2164,14 +2163,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44986</v>
+        <v>45244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2185,11 +2184,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2229,42 +2228,46 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2278,10 +2281,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45370</v>
+        <v>45979</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2293,11 +2296,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2334,39 +2342,35 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
@@ -2390,7 +2394,7 @@
         <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2478,7 +2482,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2492,10 +2496,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45244</v>
+        <v>44889</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2509,21 +2513,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>0.7</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2537,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2549,43 +2553,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3286,7 +3286,7 @@
         <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3357,14 +3357,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,11 +3378,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44599</v>
+        <v>44937</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44840</v>
+        <v>44599</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3527,8 +3527,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3571,7 +3576,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3585,10 +3590,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45933</v>
+        <v>44916</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3600,8 +3605,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3654,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3658,10 +3668,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46041</v>
+        <v>45007</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3673,8 +3683,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3717,7 +3732,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3731,10 +3746,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46041</v>
+        <v>45027</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3746,8 +3761,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3790,7 +3810,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3800,14 +3820,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44840</v>
+        <v>46077</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3820,7 +3840,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3863,7 +3883,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3873,14 +3893,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45019</v>
+        <v>46079</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3892,13 +3912,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3941,7 +3956,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3955,10 +3970,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45379</v>
+        <v>46079</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3971,7 +3986,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4014,7 +4029,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4024,14 +4039,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44680</v>
+        <v>46079</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,7 +4059,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7.7</v>
+        <v>5.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4087,7 +4102,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4097,14 +4112,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45968</v>
+        <v>46079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4116,13 +4131,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4165,7 +4175,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4179,10 +4189,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45968</v>
+        <v>45344</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4194,13 +4204,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4243,7 +4248,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4257,10 +4262,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45979</v>
+        <v>46090</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4272,13 +4277,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4321,7 +4321,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45979</v>
+        <v>44599</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4350,13 +4350,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>3.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4399,7 +4394,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4413,10 +4408,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45979</v>
+        <v>45835</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4428,13 +4423,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4477,7 +4467,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4487,14 +4477,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46077</v>
+        <v>45832</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4507,7 +4497,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.8</v>
+        <v>3.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4550,7 +4540,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4564,10 +4554,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46079</v>
+        <v>45007</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4579,8 +4569,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4623,7 +4618,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4637,10 +4632,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45988</v>
+        <v>46139</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4652,13 +4647,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4701,7 +4691,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4711,14 +4701,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46079</v>
+        <v>45933</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4731,7 +4721,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4774,7 +4764,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4784,14 +4774,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46079</v>
+        <v>44916</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4803,8 +4793,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4847,7 +4842,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4857,14 +4852,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46079</v>
+        <v>45379</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4877,7 +4872,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.2</v>
+        <v>3.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4920,7 +4915,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4934,10 +4929,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46090</v>
+        <v>46079</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4950,7 +4945,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4993,7 +4988,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5003,14 +4998,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45537</v>
+        <v>45373</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5022,13 +5017,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5071,7 +5061,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5081,14 +5071,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45537</v>
+        <v>45553</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5100,13 +5090,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5149,7 +5134,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5163,10 +5148,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46139</v>
+        <v>45968</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5178,8 +5163,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5222,7 +5212,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5236,10 +5226,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45835</v>
+        <v>45968</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5249,6 +5239,11 @@
       <c r="G55" t="inlineStr">
         <is>
           <t>TROSA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -5295,7 +5290,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5305,14 +5300,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45832</v>
+        <v>45736</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5325,7 +5320,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5368,7 +5363,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5382,10 +5377,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45373</v>
+        <v>45979</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5399,11 +5394,11 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5446,7 +5441,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5460,10 +5455,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44756</v>
+        <v>45979</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5475,8 +5470,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5519,7 +5519,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5533,10 +5533,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45527</v>
+        <v>45979</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5548,8 +5548,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5592,7 +5597,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5606,10 +5611,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44916</v>
+        <v>44840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5621,13 +5626,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5670,7 +5670,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5684,10 +5684,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45007</v>
+        <v>45988</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5748,7 +5748,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46079</v>
+        <v>45280</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44599</v>
+        <v>46273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,13 +5850,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5899,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5913,10 +5908,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44916</v>
+        <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5928,13 +5923,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5977,7 +5967,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5991,10 +5981,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45553</v>
+        <v>44680</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6007,7 +5997,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>7.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6050,7 +6040,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6064,10 +6054,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44937</v>
+        <v>46041</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6080,7 +6070,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.1</v>
+        <v>3.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6123,7 +6113,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6137,10 +6127,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45344</v>
+        <v>46041</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6153,7 +6143,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6196,7 +6186,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6210,10 +6200,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45370</v>
+        <v>45016</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6225,8 +6215,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>9.5</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6269,7 +6264,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6279,14 +6274,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45027</v>
+        <v>45537</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6300,11 +6295,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6347,7 +6342,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6361,10 +6356,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45373</v>
+        <v>45007</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6378,11 +6373,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6425,7 +6420,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6442,7 +6437,7 @@
         <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6454,8 +6449,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6508,14 +6508,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45736</v>
+        <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6527,8 +6527,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6571,7 +6576,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6585,10 +6590,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45280</v>
+        <v>44937</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6601,7 +6606,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6644,7 +6649,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6658,10 +6663,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6679,7 +6684,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6722,7 +6727,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6739,7 +6744,7 @@
         <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6757,7 +6762,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6800,7 +6805,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6814,10 +6819,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46273</v>
+        <v>45370</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6830,7 +6835,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.4</v>
+        <v>9.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6873,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6887,10 +6892,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45007</v>
+        <v>44756</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6902,13 +6907,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44937</v>
+        <v>45527</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7041,7 +7041,7 @@
         <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45370</v>
+        <v>44889</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,11 +1858,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1899,46 +1904,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1948,14 +1949,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46077</v>
+        <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1967,8 +1968,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1977,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1995,7 +2001,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2008,35 +2014,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
@@ -2060,7 +2066,7 @@
         <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2153,7 +2159,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,14 +2169,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45244</v>
+        <v>46077</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,26 +2188,21 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2212,10 +2213,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2224,50 +2225,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2281,10 +2278,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45979</v>
+        <v>45370</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2296,16 +2293,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2342,42 +2334,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2387,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46220</v>
+        <v>45244</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,17 +2402,22 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2431,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2443,46 +2444,50 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2496,10 +2501,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44889</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2511,13 +2516,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2557,35 +2557,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 29943-2022</t>
+          <t>A 25851-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44756</v>
+        <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>11.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 25851-2022</t>
+          <t>A 29943-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2899,14 +2899,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44733</v>
+        <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45537</v>
+        <v>45007</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3357,14 +3357,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45537</v>
+        <v>44599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3376,13 +3376,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3420,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3435,14 +3430,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44937</v>
+        <v>45537</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3454,8 +3449,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>7.1</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44599</v>
+        <v>44840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3527,13 +3527,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3576,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3590,10 +3585,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44916</v>
+        <v>45379</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3605,13 +3600,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>3.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3654,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3668,10 +3658,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45007</v>
+        <v>44840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3683,13 +3673,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3732,7 +3717,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3746,10 +3731,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45027</v>
+        <v>45019</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3767,7 +3752,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3810,7 +3795,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3820,14 +3805,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46077</v>
+        <v>44680</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3840,7 +3825,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>7.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3883,7 +3868,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3893,14 +3878,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46079</v>
+        <v>45835</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3913,7 +3898,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3956,7 +3941,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3970,10 +3955,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46079</v>
+        <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3986,7 +3971,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4029,7 +4014,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4039,14 +4024,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46079</v>
+        <v>45933</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4059,7 +4044,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4102,7 +4087,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4116,10 +4101,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46079</v>
+        <v>45537</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4131,8 +4116,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4175,7 +4165,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4185,14 +4175,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45344</v>
+        <v>45537</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4204,8 +4194,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4248,7 +4243,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4262,10 +4257,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46090</v>
+        <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4277,8 +4272,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4321,7 +4321,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4335,10 +4335,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44599</v>
+        <v>45968</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4350,8 +4350,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4394,7 +4399,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4408,10 +4413,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45835</v>
+        <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4423,8 +4428,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4467,7 +4477,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4481,10 +4491,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45832</v>
+        <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4496,8 +4506,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4540,7 +4555,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4554,10 +4569,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45007</v>
+        <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4571,11 +4586,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4618,7 +4633,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4632,10 +4647,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46139</v>
+        <v>45373</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4647,8 +4662,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4691,7 +4711,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4705,10 +4725,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45933</v>
+        <v>44756</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4721,7 +4741,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4764,7 +4784,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4778,10 +4798,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44916</v>
+        <v>45988</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4795,11 +4815,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4842,7 +4862,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4856,10 +4876,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45379</v>
+        <v>45527</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4872,7 +4892,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4932,7 +4952,7 @@
         <v>46079</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4988,7 +5008,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5002,10 +5022,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45373</v>
+        <v>44916</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5017,8 +5037,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5061,7 +5086,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5075,10 +5100,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45553</v>
+        <v>45007</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5090,8 +5115,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5134,7 +5164,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5148,10 +5178,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45968</v>
+        <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5169,7 +5199,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5212,7 +5242,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5226,10 +5256,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45968</v>
+        <v>44916</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5243,11 +5273,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5290,7 +5320,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5300,14 +5330,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45736</v>
+        <v>45553</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5320,7 +5350,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5363,7 +5393,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5377,10 +5407,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45979</v>
+        <v>46041</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5392,13 +5422,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5441,7 +5466,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5455,10 +5480,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45979</v>
+        <v>46041</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5470,13 +5495,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5519,7 +5539,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5533,10 +5553,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45979</v>
+        <v>44937</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5548,13 +5568,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5597,7 +5612,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5611,10 +5626,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44840</v>
+        <v>45344</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5670,7 +5685,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5684,10 +5699,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45988</v>
+        <v>45370</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5699,13 +5714,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>9.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5748,7 +5758,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5762,10 +5772,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45280</v>
+        <v>45027</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5777,8 +5787,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5836,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5831,14 +5846,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46273</v>
+        <v>46077</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5851,7 +5866,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.4</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5909,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5908,10 +5923,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44840</v>
+        <v>46079</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5924,7 +5939,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5967,7 +5982,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5977,14 +5992,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44680</v>
+        <v>46079</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5997,7 +6012,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.7</v>
+        <v>1.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6040,7 +6055,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6050,14 +6065,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46041</v>
+        <v>46079</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6070,7 +6085,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6113,7 +6128,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6123,14 +6138,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46041</v>
+        <v>46079</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6143,7 +6158,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6186,7 +6201,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6200,10 +6215,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45016</v>
+        <v>45373</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6217,11 +6232,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6264,7 +6279,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6274,14 +6289,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45537</v>
+        <v>45373</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6293,13 +6308,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6342,7 +6352,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6356,10 +6366,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45007</v>
+        <v>46090</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6371,13 +6381,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>5.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6420,7 +6425,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6430,14 +6435,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45373</v>
+        <v>45736</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6449,13 +6454,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6512,10 +6512,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45373</v>
+        <v>46139</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6527,13 +6527,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>8.199999999999999</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6576,7 +6571,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6590,10 +6585,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44937</v>
+        <v>45280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6606,7 +6601,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6649,7 +6644,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6663,10 +6658,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45019</v>
+        <v>45016</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6684,7 +6679,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6727,7 +6722,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6744,7 +6739,7 @@
         <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6762,7 +6757,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6805,7 +6800,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6819,10 +6814,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45370</v>
+        <v>45007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6834,8 +6829,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>9.5</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44756</v>
+        <v>44937</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6961,14 +6961,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45527</v>
+        <v>45593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45593</v>
+        <v>46273</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44889</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>46077</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45370</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>45244</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45007</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>44599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45537</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>45379</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>44840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45019</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44680</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45835</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>45933</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>45537</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4182,7 +4182,7 @@
         <v>45537</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4260,7 +4260,7 @@
         <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>45968</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45373</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>44756</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45988</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45527</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>46079</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>44916</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>45007</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>44916</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45553</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>46041</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5483,7 +5483,7 @@
         <v>46041</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>44937</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>45344</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>45370</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45027</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>46077</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
         <v>46079</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>46079</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>46079</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>46079</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45373</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45373</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>46090</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>45736</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>46139</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45016</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>44937</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>45593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>46273</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44889</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>46077</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45370</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45244</v>
+        <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2402,23 +2402,18 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2432,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2444,50 +2439,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2501,10 +2492,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,17 +2507,22 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2541,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2553,39 +2549,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25851-2022</t>
+          <t>A 29943-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44733</v>
+        <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 29943-2022</t>
+          <t>A 25851-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2899,14 +2899,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44756</v>
+        <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.4</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44599</v>
+        <v>45007</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3376,8 +3376,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3420,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3430,14 +3435,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45537</v>
+        <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3449,13 +3454,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3515,7 +3515,7 @@
         <v>44840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45379</v>
+        <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44840</v>
+        <v>45019</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3673,8 +3673,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3717,7 +3722,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3731,10 +3736,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45019</v>
+        <v>45379</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3746,13 +3751,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44680</v>
+        <v>46139</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.7</v>
+        <v>1.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3868,7 +3868,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45835</v>
+        <v>44680</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>7.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3955,10 +3955,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45832</v>
+        <v>45835</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4028,10 +4028,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45933</v>
+        <v>45832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,7 +4044,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4087,7 +4087,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4097,14 +4097,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45537</v>
+        <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4116,13 +4116,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4165,7 +4160,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4175,14 +4170,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45537</v>
+        <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4194,13 +4189,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4260,7 +4250,7 @@
         <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4338,7 +4328,7 @@
         <v>45968</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4416,7 +4406,7 @@
         <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4494,7 +4484,7 @@
         <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4572,7 +4562,7 @@
         <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4633,7 +4623,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4643,14 +4633,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45373</v>
+        <v>45537</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4664,11 +4654,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4711,7 +4701,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4721,14 +4711,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44756</v>
+        <v>45537</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4740,8 +4730,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4801,7 +4796,7 @@
         <v>45988</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4862,7 +4857,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4876,10 +4871,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45527</v>
+        <v>45373</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4891,8 +4886,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4935,7 +4935,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46079</v>
+        <v>44756</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44916</v>
+        <v>46041</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5037,13 +5037,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5086,7 +5081,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5100,10 +5095,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45007</v>
+        <v>46041</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5115,13 +5110,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5164,7 +5154,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5178,10 +5168,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44599</v>
+        <v>45527</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5193,13 +5183,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5242,7 +5227,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5259,7 +5244,7 @@
         <v>44916</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5277,7 +5262,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5320,7 +5305,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5334,10 +5319,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45553</v>
+        <v>45007</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5349,8 +5334,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5393,7 +5383,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5403,14 +5393,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46041</v>
+        <v>46077</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5423,7 +5413,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5466,7 +5456,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5480,10 +5470,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46041</v>
+        <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5496,7 +5486,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5539,7 +5529,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5549,14 +5539,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44937</v>
+        <v>46079</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5569,7 +5559,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7.1</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5612,7 +5602,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5622,14 +5612,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45344</v>
+        <v>46079</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5642,7 +5632,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5685,7 +5675,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5695,14 +5685,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45370</v>
+        <v>46079</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5715,7 +5705,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9.5</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5758,7 +5748,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5772,10 +5762,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45027</v>
+        <v>46090</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5787,13 +5777,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5836,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5846,14 +5831,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46077</v>
+        <v>44599</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5865,8 +5850,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5909,7 +5899,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5923,10 +5913,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46079</v>
+        <v>44916</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5938,8 +5928,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5982,7 +5977,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5992,14 +5987,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46079</v>
+        <v>45553</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6012,7 +6007,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6055,7 +6050,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6065,14 +6060,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46079</v>
+        <v>44937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6085,7 +6080,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6128,7 +6123,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6138,14 +6133,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46079</v>
+        <v>45344</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6158,7 +6153,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6201,7 +6196,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6215,10 +6210,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45373</v>
+        <v>45370</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6230,13 +6225,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6279,7 +6269,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6293,10 +6283,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45373</v>
+        <v>45027</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6308,8 +6298,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6352,7 +6347,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6366,10 +6361,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46090</v>
+        <v>45373</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6381,8 +6376,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6425,7 +6425,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6435,14 +6435,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45736</v>
+        <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6508,14 +6508,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46139</v>
+        <v>45736</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6588,7 +6588,7 @@
         <v>45280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6658,10 +6658,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45016</v>
+        <v>46273</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6673,13 +6673,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6722,7 +6717,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6732,14 +6727,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45537</v>
+        <v>45016</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6753,11 +6748,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6800,7 +6795,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6810,14 +6805,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6831,11 +6826,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6873,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6892,10 +6887,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44937</v>
+        <v>45007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6907,8 +6902,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6961,14 +6961,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45593</v>
+        <v>44937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46273</v>
+        <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44889</v>
+        <v>45244</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1860,20 +1860,20 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>0.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1900,46 +1900,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1953,10 +1957,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45979</v>
+        <v>45370</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1968,16 +1972,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2014,42 +2013,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2059,14 +2062,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44986</v>
+        <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2080,21 +2083,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9.4</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2108,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2120,46 +2123,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2173,10 +2176,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46077</v>
+        <v>44986</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2188,11 +2191,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2201,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2213,10 +2221,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2225,46 +2233,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2278,10 +2286,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45370</v>
+        <v>44889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2293,11 +2301,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2334,46 +2347,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2383,14 +2392,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46220</v>
+        <v>46077</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2403,7 +2412,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2412,10 +2421,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2430,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2443,42 +2452,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2492,10 +2501,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45244</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2507,23 +2516,18 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2537,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2549,43 +2553,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45537</v>
+        <v>45007</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45007</v>
+        <v>45527</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3376,13 +3376,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3420,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3439,10 +3434,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44599</v>
+        <v>44916</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3454,8 +3449,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44840</v>
+        <v>45379</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3571,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44840</v>
+        <v>45373</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45019</v>
+        <v>45537</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3675,11 +3675,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3722,7 +3722,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3732,14 +3732,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45379</v>
+        <v>45537</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3751,8 +3751,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3795,7 +3800,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3809,10 +3814,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46139</v>
+        <v>44937</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3825,7 +3830,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3868,7 +3873,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3882,10 +3887,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44680</v>
+        <v>45553</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3898,7 +3903,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.7</v>
+        <v>5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3941,7 +3946,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3955,10 +3960,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45835</v>
+        <v>44599</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3970,8 +3975,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4014,7 +4024,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4028,10 +4038,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45832</v>
+        <v>44916</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4043,8 +4053,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4104,7 +4119,7 @@
         <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4160,7 +4175,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4174,10 +4189,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46079</v>
+        <v>45007</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4189,8 +4204,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4233,7 +4253,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4247,10 +4267,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45968</v>
+        <v>45027</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4268,7 +4288,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4311,7 +4331,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4325,10 +4345,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45968</v>
+        <v>45344</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4340,13 +4360,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4389,7 +4404,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4399,14 +4414,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45979</v>
+        <v>45736</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4418,13 +4433,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4467,7 +4477,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4481,10 +4491,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45979</v>
+        <v>45968</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4498,11 +4508,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4545,7 +4555,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4559,10 +4569,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45979</v>
+        <v>45968</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4576,11 +4586,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4623,7 +4633,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4633,14 +4643,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45537</v>
+        <v>44599</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4652,13 +4662,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.8</v>
+        <v>3.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4701,7 +4706,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4711,14 +4716,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45537</v>
+        <v>45979</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4779,7 +4784,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4793,10 +4798,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45988</v>
+        <v>45979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4810,11 +4815,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4857,7 +4862,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4871,10 +4876,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45373</v>
+        <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4888,11 +4893,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4935,7 +4940,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4949,10 +4954,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44756</v>
+        <v>45988</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4964,8 +4969,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5008,7 +5018,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5022,10 +5032,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46041</v>
+        <v>44840</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5038,7 +5048,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5081,7 +5091,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5095,10 +5105,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46041</v>
+        <v>45280</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5111,7 +5121,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5154,7 +5164,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5168,10 +5178,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45527</v>
+        <v>46041</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5184,7 +5194,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>3.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5227,7 +5237,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5241,10 +5251,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44916</v>
+        <v>46041</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5256,13 +5266,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5305,7 +5310,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5315,14 +5320,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45007</v>
+        <v>46077</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5334,13 +5339,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5546,7 +5546,7 @@
         <v>46079</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5602,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5619,7 +5619,7 @@
         <v>46079</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5675,7 +5675,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5685,14 +5685,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46079</v>
+        <v>44840</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
         <v>46090</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44599</v>
+        <v>44680</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,13 +5850,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5899,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5913,10 +5908,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44916</v>
+        <v>45016</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5930,11 +5925,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5977,7 +5972,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5987,14 +5982,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45553</v>
+        <v>45537</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6006,8 +6001,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44937</v>
+        <v>45007</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6079,8 +6079,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>7.1</v>
+        <v>2.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6123,7 +6128,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6137,10 +6142,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45344</v>
+        <v>45373</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6152,8 +6157,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6196,7 +6206,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6210,10 +6220,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45370</v>
+        <v>45373</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6225,8 +6235,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>9.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6269,7 +6284,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6283,10 +6298,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45027</v>
+        <v>45835</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6298,13 +6313,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6347,7 +6357,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6361,10 +6371,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45373</v>
+        <v>45832</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6376,13 +6386,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>8.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6425,7 +6430,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6439,10 +6444,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45373</v>
+        <v>44937</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6455,7 +6460,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6503,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6508,14 +6513,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45736</v>
+        <v>45019</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6527,8 +6532,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6571,7 +6581,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6581,14 +6591,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45280</v>
+        <v>45537</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6600,8 +6610,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6644,7 +6659,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6658,10 +6673,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46273</v>
+        <v>45370</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6674,7 +6689,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.4</v>
+        <v>9.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6717,7 +6732,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6731,10 +6746,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45016</v>
+        <v>44756</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6746,13 +6761,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6795,7 +6805,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6805,14 +6815,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45537</v>
+        <v>46139</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6824,13 +6834,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>6.6</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6873,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6887,10 +6892,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45007</v>
+        <v>45527</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6902,13 +6907,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6961,14 +6961,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44937</v>
+        <v>45593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45593</v>
+        <v>46079</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45527</v>
+        <v>46273</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45244</v>
+        <v>44889</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>0.7</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1900,50 +1900,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1957,10 +1953,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45370</v>
+        <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1972,11 +1968,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2013,46 +2014,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2062,14 +2059,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45979</v>
+        <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2083,20 +2080,20 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2111,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2123,46 +2120,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2176,10 +2173,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44986</v>
+        <v>46077</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2191,26 +2188,21 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2221,10 +2213,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2233,46 +2225,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2286,10 +2278,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44889</v>
+        <v>45370</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2301,16 +2293,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2347,42 +2334,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2392,14 +2383,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46077</v>
+        <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2403,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2421,10 +2412,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2439,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2452,42 +2443,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2501,10 +2492,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,17 +2507,22 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2541,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2553,39 +2549,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 29943-2022</t>
+          <t>A 25851-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44756</v>
+        <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>11.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 25851-2022</t>
+          <t>A 29943-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2899,14 +2899,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44733</v>
+        <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45527</v>
+        <v>45007</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3376,8 +3376,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3420,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3434,10 +3439,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44916</v>
+        <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3449,13 +3454,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45379</v>
+        <v>44840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3571,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45373</v>
+        <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3654,14 +3654,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45537</v>
+        <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3673,13 +3673,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3722,7 +3717,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3732,14 +3727,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45537</v>
+        <v>45019</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3753,11 +3748,11 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3800,7 +3795,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3814,10 +3809,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44937</v>
+        <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3830,7 +3825,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7.1</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3873,7 +3868,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3887,10 +3882,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45553</v>
+        <v>44680</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3903,7 +3898,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>7.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3946,7 +3941,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3960,10 +3955,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44599</v>
+        <v>45835</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3975,13 +3970,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4024,7 +4014,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4038,10 +4028,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44916</v>
+        <v>45933</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4053,13 +4043,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4102,7 +4087,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4116,10 +4101,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45933</v>
+        <v>45832</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4132,7 +4117,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4175,7 +4160,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4189,10 +4174,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45007</v>
+        <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4210,7 +4195,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4253,7 +4238,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4267,10 +4252,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45027</v>
+        <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4288,7 +4273,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4331,7 +4316,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4341,14 +4326,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45344</v>
+        <v>45537</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4360,8 +4345,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4404,7 +4394,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4418,10 +4408,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45736</v>
+        <v>45537</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4433,8 +4423,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4477,7 +4472,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4491,10 +4486,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45968</v>
+        <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4508,11 +4503,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4555,7 +4550,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4569,10 +4564,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45968</v>
+        <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4586,11 +4581,11 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4633,7 +4628,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4647,10 +4642,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44599</v>
+        <v>45979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4662,8 +4657,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4706,7 +4706,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4720,10 +4720,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45979</v>
+        <v>45988</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4737,11 +4737,11 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45979</v>
+        <v>45373</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4815,11 +4815,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45979</v>
+        <v>44756</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4891,13 +4891,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4940,7 +4935,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4954,10 +4949,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45988</v>
+        <v>46079</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4969,13 +4964,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5018,7 +5008,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5032,10 +5022,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44840</v>
+        <v>45527</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5048,7 +5038,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5091,7 +5081,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5105,10 +5095,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45280</v>
+        <v>46041</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5121,7 +5111,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5181,7 +5171,7 @@
         <v>46041</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5237,7 +5227,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5251,10 +5241,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46041</v>
+        <v>44916</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5266,8 +5256,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5310,7 +5305,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5320,14 +5315,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46077</v>
+        <v>45007</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5339,8 +5334,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5546,7 +5546,7 @@
         <v>46079</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5602,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5619,7 +5619,7 @@
         <v>46079</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5675,7 +5675,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5685,14 +5685,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44840</v>
+        <v>46079</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5765,7 +5765,7 @@
         <v>46090</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5821,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44680</v>
+        <v>44599</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,8 +5850,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5899,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5908,10 +5913,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45016</v>
+        <v>44916</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5925,11 +5930,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5972,7 +5977,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5982,14 +5987,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45537</v>
+        <v>45553</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6001,13 +6006,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45007</v>
+        <v>44937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6079,13 +6079,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>2.5</v>
+        <v>7.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6128,7 +6123,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6142,10 +6137,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45373</v>
+        <v>45344</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6157,13 +6152,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6206,7 +6196,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6220,10 +6210,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45373</v>
+        <v>45370</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6235,13 +6225,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6284,7 +6269,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6298,10 +6283,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45835</v>
+        <v>45027</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6313,8 +6298,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6357,7 +6347,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6371,10 +6361,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45832</v>
+        <v>45373</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6386,8 +6376,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6430,7 +6425,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6444,10 +6439,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44937</v>
+        <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6460,7 +6455,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6503,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6513,14 +6508,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45019</v>
+        <v>45736</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6532,13 +6527,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6581,7 +6571,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6591,14 +6581,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45537</v>
+        <v>45280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6610,13 +6600,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6659,7 +6644,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6673,10 +6658,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45370</v>
+        <v>45016</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6688,8 +6673,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>9.5</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6732,7 +6722,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6746,10 +6736,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44756</v>
+        <v>46273</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6762,7 +6752,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6805,7 +6795,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6815,14 +6805,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46139</v>
+        <v>45537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6834,8 +6824,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>6.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6873,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6892,10 +6887,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45527</v>
+        <v>45007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6907,8 +6902,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6961,14 +6961,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45593</v>
+        <v>44937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46079</v>
+        <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.6</v>
+        <v>3.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46273</v>
+        <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44889</v>
+        <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,16 +1858,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1904,42 +1899,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1949,14 +1948,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45979</v>
+        <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1968,13 +1967,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1983,10 +1977,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2001,7 +1995,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2014,35 +2008,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
@@ -2066,7 +2060,7 @@
         <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2159,7 +2153,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2169,14 +2163,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46077</v>
+        <v>45979</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2188,8 +2182,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2198,10 +2197,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2216,7 +2215,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2229,42 +2228,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2278,10 +2277,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45370</v>
+        <v>45244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2293,8 +2292,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2303,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2318,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2330,43 +2334,43 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -2390,7 +2394,7 @@
         <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2478,7 +2482,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2492,10 +2496,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45244</v>
+        <v>44889</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2509,21 +2513,21 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>0.7</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2537,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2549,43 +2553,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25851-2022</t>
+          <t>A 29943-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44733</v>
+        <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 29943-2022</t>
+          <t>A 25851-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2899,14 +2899,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44756</v>
+        <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.4</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45537</v>
+        <v>45527</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3298,13 +3298,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3342,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3357,14 +3352,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,11 +3373,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3420,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3435,14 +3430,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44599</v>
+        <v>45537</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3454,8 +3449,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44840</v>
+        <v>44937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3571,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44840</v>
+        <v>46041</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46139</v>
+        <v>46041</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45019</v>
+        <v>44599</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45379</v>
+        <v>44916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3824,8 +3824,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3868,7 +3873,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3882,10 +3887,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44680</v>
+        <v>45007</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3897,8 +3902,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3941,7 +3951,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3955,10 +3965,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45835</v>
+        <v>45027</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3970,8 +3980,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4014,7 +4029,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4024,14 +4039,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45933</v>
+        <v>46077</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4044,7 +4059,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4087,7 +4102,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4097,14 +4112,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45832</v>
+        <v>46079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4117,7 +4132,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4160,7 +4175,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4174,10 +4189,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45968</v>
+        <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4189,13 +4204,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4238,7 +4248,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4248,14 +4258,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45968</v>
+        <v>46079</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4267,13 +4277,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4316,7 +4321,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4330,10 +4335,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45537</v>
+        <v>46079</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4345,13 +4350,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4394,7 +4394,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4404,14 +4404,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45537</v>
+        <v>45933</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4423,13 +4423,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4472,7 +4467,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4486,10 +4481,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45979</v>
+        <v>46090</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4501,13 +4496,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4550,7 +4540,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4564,10 +4554,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45979</v>
+        <v>45344</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4579,13 +4569,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4628,7 +4613,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4642,10 +4627,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45979</v>
+        <v>44599</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4657,13 +4642,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4706,7 +4686,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4720,10 +4700,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45988</v>
+        <v>45968</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4741,7 +4721,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4784,7 +4764,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4798,10 +4778,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45373</v>
+        <v>45968</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4815,11 +4795,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4862,7 +4842,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4876,10 +4856,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44756</v>
+        <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4891,8 +4871,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4935,7 +4920,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4949,10 +4934,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46079</v>
+        <v>45979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4964,8 +4949,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5008,7 +4998,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5022,10 +5012,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45527</v>
+        <v>45979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5037,8 +5027,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5081,7 +5076,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5095,10 +5090,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46041</v>
+        <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5111,7 +5106,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5154,7 +5149,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5168,10 +5163,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46041</v>
+        <v>45832</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5184,7 +5179,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5227,7 +5222,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5241,10 +5236,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44916</v>
+        <v>45988</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5258,7 +5253,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -5305,7 +5300,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5322,7 +5317,7 @@
         <v>45007</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5340,7 +5335,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5383,7 +5378,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5393,14 +5388,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46077</v>
+        <v>46139</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5413,7 +5408,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5456,7 +5451,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5473,7 +5468,7 @@
         <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5486,7 +5481,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5529,7 +5524,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5539,14 +5534,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46079</v>
+        <v>44916</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5558,8 +5553,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5602,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5612,14 +5612,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46079</v>
+        <v>45379</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5675,7 +5675,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5685,14 +5685,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46079</v>
+        <v>45373</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5748,7 +5748,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5762,10 +5762,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46090</v>
+        <v>45553</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5831,14 +5831,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44599</v>
+        <v>45736</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,13 +5850,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5899,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5913,10 +5908,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44916</v>
+        <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5928,13 +5923,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5977,7 +5967,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5991,10 +5981,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45553</v>
+        <v>45280</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6007,7 +5997,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6050,7 +6040,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6064,10 +6054,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44937</v>
+        <v>46273</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6080,7 +6070,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6123,7 +6113,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6137,10 +6127,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45344</v>
+        <v>44840</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6153,7 +6143,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6196,7 +6186,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6210,10 +6200,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45370</v>
+        <v>44680</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6226,7 +6216,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6269,7 +6259,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6283,10 +6273,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45027</v>
+        <v>45016</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6304,7 +6294,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6347,7 +6337,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6357,14 +6347,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45373</v>
+        <v>45537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6378,11 +6368,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6425,7 +6415,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6439,10 +6429,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45373</v>
+        <v>45007</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6454,8 +6444,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6493,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6508,14 +6503,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45736</v>
+        <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6527,8 +6522,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45280</v>
+        <v>45373</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6600,8 +6600,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6644,7 +6649,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6658,10 +6663,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45016</v>
+        <v>44937</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6673,13 +6678,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6722,7 +6722,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46273</v>
+        <v>45019</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6751,8 +6751,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6795,7 +6800,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6812,7 +6817,7 @@
         <v>45537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6830,7 +6835,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6873,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6887,10 +6892,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45007</v>
+        <v>45370</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6902,13 +6907,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>9.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44937</v>
+        <v>44756</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45593</v>
+        <v>45527</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7107,14 +7107,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45527</v>
+        <v>45593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45979</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>44889</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45527</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45537</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45537</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>46041</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>46041</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44599</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>45007</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45027</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>46077</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>46079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>46079</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>46079</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45933</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>46090</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45344</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>44599</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45968</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45968</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>45979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>45979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>45832</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45988</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45007</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46139</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44916</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>45379</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>45373</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>45553</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45736</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45280</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>46273</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44840</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44680</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>45016</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>45537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45007</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45373</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>44937</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45019</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>45370</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>44756</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45527</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>45979</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>45244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>44889</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45527</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45537</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45537</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>46041</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>46041</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>44599</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>44916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3890,7 +3890,7 @@
         <v>45007</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>45027</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>46077</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>46079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>46079</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4338,7 +4338,7 @@
         <v>46079</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4411,7 +4411,7 @@
         <v>45933</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>46090</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45344</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>44599</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45968</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45968</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>45979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         <v>45979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>45832</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         <v>45988</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5317,7 +5317,7 @@
         <v>45007</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46139</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44916</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>45379</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>45373</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>45553</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45736</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45280</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>46273</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44840</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44680</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>45016</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>45537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>45007</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45373</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>44937</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45019</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>45370</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>44756</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45527</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45370</v>
+        <v>45979</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,11 +1858,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1899,39 +1904,35 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1956,7 @@
         <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2043,7 +2044,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2053,14 +2054,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44986</v>
+        <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,21 +2075,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2102,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2114,46 +2115,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2163,14 +2164,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45979</v>
+        <v>44986</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2184,20 +2185,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2212,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2224,46 +2225,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2277,10 +2278,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45244</v>
+        <v>45370</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2292,13 +2293,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2307,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2322,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2334,43 +2330,43 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
@@ -2394,7 +2390,7 @@
         <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2482,7 +2478,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2496,10 +2492,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44889</v>
+        <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2513,20 +2509,20 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2541,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2553,39 +2549,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45527</v>
+        <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3298,8 +3298,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3342,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3352,14 +3357,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45537</v>
+        <v>45007</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3373,11 +3378,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3420,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3430,14 +3435,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45537</v>
+        <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3449,13 +3454,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44937</v>
+        <v>45527</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3571,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46041</v>
+        <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46041</v>
+        <v>45933</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44599</v>
+        <v>45968</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3795,7 +3795,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3809,10 +3809,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44916</v>
+        <v>45968</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3826,11 +3826,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3873,7 +3873,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3887,10 +3887,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45007</v>
+        <v>45979</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -3951,7 +3951,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45027</v>
+        <v>45979</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3982,11 +3982,11 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.6</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4039,14 +4039,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46077</v>
+        <v>46041</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8</v>
+        <v>6.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4112,14 +4112,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46079</v>
+        <v>46041</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46079</v>
+        <v>45979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4204,8 +4204,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4248,7 +4253,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4258,14 +4263,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46079</v>
+        <v>44840</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4278,7 +4283,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.3</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4321,7 +4326,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4331,14 +4336,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46079</v>
+        <v>45019</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4350,8 +4355,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4394,7 +4404,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4408,10 +4418,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45933</v>
+        <v>45379</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4424,7 +4434,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4467,7 +4477,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4481,10 +4491,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46090</v>
+        <v>45988</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4496,8 +4506,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4540,7 +4555,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4554,10 +4569,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45344</v>
+        <v>44680</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4570,7 +4585,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4613,7 +4628,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4623,14 +4638,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44599</v>
+        <v>46077</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4643,7 +4658,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4686,7 +4701,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4700,10 +4715,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45968</v>
+        <v>46079</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4715,13 +4730,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4764,7 +4774,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4774,14 +4784,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45968</v>
+        <v>46079</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4793,13 +4803,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4842,7 +4847,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4852,14 +4857,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45979</v>
+        <v>46079</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4871,13 +4876,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4920,7 +4920,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4930,14 +4930,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45979</v>
+        <v>46079</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4949,13 +4949,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4998,7 +4993,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5012,10 +5007,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45979</v>
+        <v>46090</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5027,13 +5022,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5076,7 +5066,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5086,14 +5076,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45835</v>
+        <v>45537</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5105,8 +5095,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5149,7 +5144,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5159,14 +5154,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45832</v>
+        <v>45537</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5178,8 +5173,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45988</v>
+        <v>46139</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5251,13 +5251,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5300,7 +5295,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5314,10 +5309,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45007</v>
+        <v>45835</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5329,13 +5324,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5378,7 +5368,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5392,10 +5382,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46139</v>
+        <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5408,7 +5398,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5451,7 +5441,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5465,10 +5455,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46079</v>
+        <v>45373</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5480,8 +5470,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5524,7 +5519,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5538,10 +5533,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44916</v>
+        <v>44756</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5553,13 +5548,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5592,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5616,10 +5606,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45379</v>
+        <v>45527</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5632,7 +5622,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5675,7 +5665,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5689,10 +5679,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45373</v>
+        <v>44916</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5704,8 +5694,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5748,7 +5743,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5762,10 +5757,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45553</v>
+        <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5777,8 +5772,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5831,14 +5831,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45736</v>
+        <v>46079</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44840</v>
+        <v>44599</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5923,8 +5923,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5967,7 +5972,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5981,10 +5986,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45280</v>
+        <v>44916</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5996,8 +6001,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6040,7 +6050,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6054,10 +6064,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46273</v>
+        <v>45553</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6070,7 +6080,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6113,7 +6123,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6127,10 +6137,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44840</v>
+        <v>44937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6143,7 +6153,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6186,7 +6196,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6200,10 +6210,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44680</v>
+        <v>45344</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6216,7 +6226,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6259,7 +6269,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6273,10 +6283,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45016</v>
+        <v>45370</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6288,13 +6298,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>9.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6337,7 +6342,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6347,14 +6352,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45537</v>
+        <v>45027</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6368,11 +6373,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6415,7 +6420,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6429,10 +6434,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45007</v>
+        <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6446,11 +6451,11 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6493,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6510,7 +6515,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6522,13 +6527,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6581,14 +6581,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45373</v>
+        <v>45736</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6600,13 +6600,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6649,7 +6644,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6663,10 +6658,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44937</v>
+        <v>45280</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6679,7 +6674,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6722,7 +6717,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6736,10 +6731,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45019</v>
+        <v>45016</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6757,7 +6752,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6800,7 +6795,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6817,7 +6812,7 @@
         <v>45537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6835,7 +6830,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>6.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6873,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6892,10 +6887,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45370</v>
+        <v>46273</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6908,7 +6903,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>9.5</v>
+        <v>4.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6946,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6960,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44756</v>
+        <v>45007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6980,8 +6975,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45527</v>
+        <v>44937</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>45593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45979</v>
+        <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,16 +1858,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1904,42 +1899,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1953,10 +1952,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46077</v>
+        <v>44986</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1968,11 +1967,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1981,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1993,10 +1997,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2005,46 +2009,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2062,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44889</v>
+        <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2075,11 +2079,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2119,42 +2123,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2168,10 +2172,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44986</v>
+        <v>46077</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2183,26 +2187,21 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2213,10 +2212,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2225,46 +2224,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2278,10 +2277,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45370</v>
+        <v>45244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2293,8 +2292,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2303,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2318,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2330,50 +2334,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46220</v>
+        <v>44889</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2402,8 +2406,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2443,42 +2452,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2492,10 +2501,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45244</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2507,23 +2516,18 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2537,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2549,43 +2553,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 63049-2021</t>
+          <t>A 3134-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44505</v>
+        <v>44582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3071,11 +3071,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3134-2022</t>
+          <t>A 63049-2021</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44582</v>
+        <v>44505</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,11 +3149,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45537</v>
+        <v>45527</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3298,13 +3298,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3342,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3357,14 +3352,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,11 +3373,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3420,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3435,14 +3430,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44599</v>
+        <v>45537</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3454,8 +3449,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45527</v>
+        <v>44937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>7.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3571,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3585,10 +3585,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44840</v>
+        <v>44599</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3600,8 +3600,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3649,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3658,10 +3663,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45933</v>
+        <v>44916</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3673,8 +3678,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3717,7 +3727,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3731,10 +3741,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45968</v>
+        <v>45007</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3752,7 +3762,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3795,7 +3805,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3809,10 +3819,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45968</v>
+        <v>46041</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3824,13 +3834,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3873,7 +3878,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3887,10 +3892,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45979</v>
+        <v>45027</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3904,11 +3909,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3951,7 +3956,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3965,10 +3970,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45979</v>
+        <v>46041</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3980,13 +3985,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>6.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46041</v>
+        <v>45933</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4116,10 +4116,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46041</v>
+        <v>45344</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4175,7 +4175,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45979</v>
+        <v>44599</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4204,13 +4204,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4253,7 +4248,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4267,10 +4262,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44840</v>
+        <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4282,8 +4277,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45019</v>
+        <v>45968</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4418,10 +4418,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45379</v>
+        <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4433,8 +4433,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4477,7 +4482,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4491,10 +4496,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45988</v>
+        <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4508,11 +4513,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4555,7 +4560,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4569,10 +4574,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44680</v>
+        <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4584,8 +4589,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4645,7 +4655,7 @@
         <v>46077</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4701,7 +4711,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4715,10 +4725,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46079</v>
+        <v>45988</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4730,8 +4740,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.9</v>
+        <v>0.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4774,7 +4789,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4791,7 +4806,7 @@
         <v>46079</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4804,7 +4819,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4847,7 +4862,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4857,14 +4872,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
         <v>46079</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4877,7 +4892,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4920,7 +4935,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4937,7 +4952,7 @@
         <v>46079</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4950,7 +4965,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4993,7 +5008,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5003,14 +5018,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46090</v>
+        <v>46079</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5023,7 +5038,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5066,7 +5081,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5076,14 +5091,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45537</v>
+        <v>46090</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5095,13 +5110,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>1.8</v>
+        <v>5.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5144,7 +5154,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5154,14 +5164,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45537</v>
+        <v>45007</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5175,11 +5185,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5222,7 +5232,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5236,10 +5246,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46139</v>
+        <v>44916</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5249,6 +5259,11 @@
       <c r="G55" t="inlineStr">
         <is>
           <t>TROSA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -5312,7 +5327,7 @@
         <v>45835</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5385,7 +5400,7 @@
         <v>45832</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5441,7 +5456,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5455,10 +5470,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45373</v>
+        <v>45379</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5470,13 +5485,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5519,7 +5529,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5533,10 +5543,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44756</v>
+        <v>45373</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5549,7 +5559,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5592,7 +5602,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5606,10 +5616,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45527</v>
+        <v>45553</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5622,7 +5632,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5665,7 +5675,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5679,10 +5689,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44916</v>
+        <v>46139</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5694,13 +5704,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5743,7 +5748,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5753,14 +5758,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45007</v>
+        <v>45736</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5772,13 +5777,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5838,7 +5838,7 @@
         <v>46079</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44599</v>
+        <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5923,13 +5923,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5972,7 +5967,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5986,10 +5981,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44916</v>
+        <v>45280</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6001,13 +5996,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6050,7 +6040,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6064,10 +6054,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45553</v>
+        <v>44840</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6080,7 +6070,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6123,7 +6113,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6137,10 +6127,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44937</v>
+        <v>44680</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6153,7 +6143,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6196,7 +6186,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6210,10 +6200,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45344</v>
+        <v>45016</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6225,8 +6215,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6269,7 +6264,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6279,14 +6274,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45370</v>
+        <v>45537</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6298,8 +6293,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45027</v>
+        <v>45007</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6437,7 +6437,7 @@
         <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6515,7 +6515,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6527,8 +6527,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6571,7 +6576,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6581,14 +6586,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45736</v>
+        <v>44937</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6601,7 +6606,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6644,7 +6649,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6658,10 +6663,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45280</v>
+        <v>46273</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6674,7 +6679,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6717,7 +6722,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6731,10 +6736,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6752,7 +6757,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6795,7 +6800,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6812,7 +6817,7 @@
         <v>45537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6830,7 +6835,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6873,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6887,10 +6892,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46273</v>
+        <v>45370</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6903,7 +6908,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.4</v>
+        <v>9.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6946,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6960,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45007</v>
+        <v>44756</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6975,13 +6980,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44937</v>
+        <v>45527</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>45593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 11736-2024</t>
+          <t>A 51481-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45373</v>
+        <v>45603</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1534,13 +1534,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>12.8</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1570,154 +1570,154 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Talltita
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 51481-2024 artfynd.xlsx", "A 51481-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 51481-2024 karta.png", "A 51481-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 51481-2024 georefererad karta.tif", "A 51481-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 51481-2024 FSC-klagomål.docx", "A 51481-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 51481-2024 FSC-klagomål mail.docx", "A 51481-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 51481-2024 tillsynsbegäran.docx", "A 51481-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 51481-2024 tillsynsbegäran mail.docx", "A 51481-2024")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 51481-2024 prioriterade fågelarter.docx", "A 51481-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 11736-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45373</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TROSA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Enkelbeckasin
 Grön sköldmossa</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11736-2024 artfynd.xlsx", "A 11736-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11736-2024 karta.png", "A 11736-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11736-2024 georefererad karta.tif", "A 11736-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11736-2024 FSC-klagomål.docx", "A 11736-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11736-2024 FSC-klagomål mail.docx", "A 11736-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11736-2024 tillsynsbegäran.docx", "A 11736-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11736-2024 tillsynsbegäran mail.docx", "A 11736-2024")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11736-2024 prioriterade fågelarter.docx", "A 11736-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 51481-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45603</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TROSA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Talltita
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 51481-2024 artfynd.xlsx", "A 51481-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 51481-2024 karta.png", "A 51481-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 51481-2024 georefererad karta.tif", "A 51481-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 51481-2024 FSC-klagomål.docx", "A 51481-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 51481-2024 FSC-klagomål mail.docx", "A 51481-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 51481-2024 tillsynsbegäran.docx", "A 51481-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 51481-2024 tillsynsbegäran mail.docx", "A 51481-2024")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 51481-2024 prioriterade fågelarter.docx", "A 51481-2024")</f>
         <v/>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45370</v>
+        <v>45244</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,8 +1858,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1868,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1883,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1895,43 +1900,43 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -1955,7 +1960,7 @@
         <v>44986</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2048,7 +2053,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2062,10 +2067,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45979</v>
+        <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,11 +2084,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2123,42 +2128,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2168,14 +2173,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46077</v>
+        <v>45370</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2188,19 +2193,19 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2215,7 +2220,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2228,42 +2233,46 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2277,10 +2286,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45244</v>
+        <v>45979</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2294,21 +2303,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2322,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2334,50 +2343,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2392,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44889</v>
+        <v>46077</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,13 +2411,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2421,10 +2421,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2452,35 +2452,35 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
         <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3134-2022</t>
+          <t>A 63049-2021</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44582</v>
+        <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3071,11 +3071,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 63049-2021</t>
+          <t>A 6109-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44505</v>
+        <v>44599</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,13 +3147,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3196,7 +3191,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 6109-2022</t>
+          <t>A 3134-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3210,10 +3205,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44599</v>
+        <v>44582</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3225,8 +3220,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45527</v>
+        <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3298,8 +3298,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3342,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3352,14 +3357,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45537</v>
+        <v>44916</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3377,7 +3382,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3420,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3430,14 +3435,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45537</v>
+        <v>45007</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3451,11 +3456,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3503,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3517,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44937</v>
+        <v>44599</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3528,7 +3533,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3571,7 +3576,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3585,10 +3590,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44599</v>
+        <v>45016</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3606,7 +3611,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3649,7 +3654,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3663,10 +3668,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44916</v>
+        <v>45007</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3680,11 +3685,11 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3727,7 +3732,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3741,10 +3746,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45007</v>
+        <v>44840</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3756,13 +3761,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3805,7 +3805,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46041</v>
+        <v>45019</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3834,8 +3834,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3878,7 +3883,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3892,10 +3897,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45027</v>
+        <v>45379</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3907,13 +3912,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46041</v>
+        <v>44680</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.3</v>
+        <v>7.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4039,14 +4039,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45933</v>
+        <v>45537</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4058,8 +4058,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>6.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4102,7 +4107,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4116,10 +4121,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45344</v>
+        <v>44599</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4131,8 +4136,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4175,7 +4185,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4189,10 +4199,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44599</v>
+        <v>44916</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4204,8 +4214,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4248,7 +4263,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4262,10 +4277,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45968</v>
+        <v>45553</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4277,13 +4292,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4326,7 +4336,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4340,10 +4350,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45968</v>
+        <v>45007</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4361,7 +4371,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4404,7 +4414,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4418,10 +4428,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45979</v>
+        <v>44937</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4433,13 +4443,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4482,7 +4487,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4496,10 +4501,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45979</v>
+        <v>45344</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4511,13 +4516,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45979</v>
+        <v>45370</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4589,13 +4589,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>9.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4638,7 +4633,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4648,14 +4643,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46077</v>
+        <v>44937</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4668,7 +4663,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4711,7 +4706,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4725,10 +4720,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45988</v>
+        <v>45027</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4746,7 +4741,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.6</v>
+        <v>4.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4789,7 +4784,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4803,10 +4798,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46079</v>
+        <v>45593</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4819,7 +4814,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4862,7 +4857,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4876,10 +4871,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46079</v>
+        <v>45373</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4891,8 +4886,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4935,7 +4935,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4945,14 +4945,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46079</v>
+        <v>45373</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5018,14 +5018,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46079</v>
+        <v>45527</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5081,7 +5081,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46090</v>
+        <v>44840</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5.1</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5164,14 +5164,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5185,11 +5185,11 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5242,14 +5242,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44916</v>
+        <v>45537</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5310,7 +5310,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5320,14 +5320,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45835</v>
+        <v>45736</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45832</v>
+        <v>45280</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45379</v>
+        <v>45373</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5485,8 +5485,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5529,7 +5534,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5543,10 +5548,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45373</v>
+        <v>44756</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5559,7 +5564,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5607,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5616,10 +5621,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45553</v>
+        <v>45527</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5632,7 +5637,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5675,7 +5680,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5689,10 +5694,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46139</v>
+        <v>45968</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5704,8 +5709,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5748,7 +5758,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5758,14 +5768,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45736</v>
+        <v>45968</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5777,8 +5787,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5836,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5850,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46079</v>
+        <v>45979</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,8 +5865,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5914,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5908,10 +5928,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44840</v>
+        <v>45979</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5923,8 +5943,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5967,7 +5992,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5981,10 +6006,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45280</v>
+        <v>45979</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5996,8 +6021,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6040,7 +6070,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6054,10 +6084,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44840</v>
+        <v>45933</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6070,7 +6100,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6113,7 +6143,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6127,10 +6157,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44680</v>
+        <v>45988</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6142,8 +6172,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6186,7 +6221,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6200,10 +6235,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45016</v>
+        <v>46041</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6215,13 +6250,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6264,7 +6294,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6274,14 +6304,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45537</v>
+        <v>46041</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6293,13 +6323,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6342,7 +6367,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6352,14 +6377,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45007</v>
+        <v>46077</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6371,13 +6396,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6420,7 +6440,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6434,10 +6454,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45373</v>
+        <v>46079</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6449,13 +6469,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6513,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6508,14 +6523,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45373</v>
+        <v>46079</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6527,13 +6542,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>8.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6576,7 +6586,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6586,14 +6596,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44937</v>
+        <v>46079</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6606,7 +6616,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6649,7 +6659,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6659,14 +6669,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46273</v>
+        <v>46079</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6679,7 +6689,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6722,7 +6732,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6736,10 +6746,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45019</v>
+        <v>46090</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6751,13 +6761,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6800,7 +6805,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6810,14 +6815,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45537</v>
+        <v>46139</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6829,13 +6834,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45370</v>
+        <v>45835</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44756</v>
+        <v>45832</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45527</v>
+        <v>46079</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>5.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7107,14 +7107,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45593</v>
+        <v>46273</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 51481-2024</t>
+          <t>A 11736-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45603</v>
+        <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1534,13 +1534,13 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>12.8</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1570,154 +1570,154 @@
         <v>2</v>
       </c>
       <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin
+Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="W10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11736-2024 artfynd.xlsx", "A 11736-2024")</f>
+        <v/>
+      </c>
+      <c r="X10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11736-2024 karta.png", "A 11736-2024")</f>
+        <v/>
+      </c>
+      <c r="Y10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11736-2024 georefererad karta.tif", "A 11736-2024")</f>
+        <v/>
+      </c>
+      <c r="AA10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11736-2024 FSC-klagomål.docx", "A 11736-2024")</f>
+        <v/>
+      </c>
+      <c r="AB10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11736-2024 FSC-klagomål mail.docx", "A 11736-2024")</f>
+        <v/>
+      </c>
+      <c r="AC10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11736-2024 tillsynsbegäran.docx", "A 11736-2024")</f>
+        <v/>
+      </c>
+      <c r="AD10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11736-2024 tillsynsbegäran mail.docx", "A 11736-2024")</f>
+        <v/>
+      </c>
+      <c r="AE10">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11736-2024 prioriterade fågelarter.docx", "A 11736-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A 51481-2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>45603</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SÖDERMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>TROSA</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="2" t="inlineStr">
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>Talltita
 Spillkråka</t>
         </is>
       </c>
-      <c r="W10">
+      <c r="W11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 51481-2024 artfynd.xlsx", "A 51481-2024")</f>
         <v/>
       </c>
-      <c r="X10">
+      <c r="X11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 51481-2024 karta.png", "A 51481-2024")</f>
         <v/>
       </c>
-      <c r="Y10">
+      <c r="Y11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 51481-2024 georefererad karta.tif", "A 51481-2024")</f>
         <v/>
       </c>
-      <c r="AA10">
+      <c r="AA11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 51481-2024 FSC-klagomål.docx", "A 51481-2024")</f>
         <v/>
       </c>
-      <c r="AB10">
+      <c r="AB11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 51481-2024 FSC-klagomål mail.docx", "A 51481-2024")</f>
         <v/>
       </c>
-      <c r="AC10">
+      <c r="AC11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 51481-2024 tillsynsbegäran.docx", "A 51481-2024")</f>
         <v/>
       </c>
-      <c r="AD10">
+      <c r="AD11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 51481-2024 tillsynsbegäran mail.docx", "A 51481-2024")</f>
         <v/>
       </c>
-      <c r="AE10">
+      <c r="AE11">
         <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 51481-2024 prioriterade fågelarter.docx", "A 51481-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A 11736-2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>45373</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>TROSA</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>Enkelbeckasin
-Grön sköldmossa</t>
-        </is>
-      </c>
-      <c r="W11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11736-2024 artfynd.xlsx", "A 11736-2024")</f>
-        <v/>
-      </c>
-      <c r="X11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11736-2024 karta.png", "A 11736-2024")</f>
-        <v/>
-      </c>
-      <c r="Y11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11736-2024 georefererad karta.tif", "A 11736-2024")</f>
-        <v/>
-      </c>
-      <c r="AA11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11736-2024 FSC-klagomål.docx", "A 11736-2024")</f>
-        <v/>
-      </c>
-      <c r="AB11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11736-2024 FSC-klagomål mail.docx", "A 11736-2024")</f>
-        <v/>
-      </c>
-      <c r="AC11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11736-2024 tillsynsbegäran.docx", "A 11736-2024")</f>
-        <v/>
-      </c>
-      <c r="AD11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11736-2024 tillsynsbegäran mail.docx", "A 11736-2024")</f>
-        <v/>
-      </c>
-      <c r="AE11">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11736-2024 prioriterade fågelarter.docx", "A 11736-2024")</f>
         <v/>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45244</v>
+        <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,13 +1858,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1873,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1888,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1900,50 +1895,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1957,10 +1952,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44986</v>
+        <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1972,26 +1967,21 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -2002,10 +1992,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2014,46 +2004,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2067,10 +2057,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44889</v>
+        <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2084,11 +2074,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2128,42 +2118,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2173,14 +2163,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45370</v>
+        <v>44986</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2192,8 +2182,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>9.4</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -2202,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2217,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2229,50 +2224,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2286,10 +2277,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45979</v>
+        <v>45244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2303,20 +2294,20 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2331,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2343,46 +2334,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2392,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46077</v>
+        <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2407,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2421,10 +2416,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2439,7 +2434,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2452,42 +2447,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2501,10 +2496,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>44889</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,8 +2511,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2557,35 +2557,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 6109-2022</t>
+          <t>A 3134-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3132,10 +3132,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44599</v>
+        <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,8 +3147,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3191,7 +3196,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 3134-2022</t>
+          <t>A 6109-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3205,10 +3210,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44582</v>
+        <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3220,13 +3225,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45537</v>
+        <v>45527</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3298,13 +3298,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3342,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3361,10 +3356,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44916</v>
+        <v>46041</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3376,13 +3371,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3415,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3439,10 +3429,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45007</v>
+        <v>46041</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3454,13 +3444,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3503,7 +3488,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3513,14 +3498,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44599</v>
+        <v>45537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3532,8 +3517,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3.7</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3576,7 +3566,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3586,14 +3576,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45016</v>
+        <v>45537</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3607,11 +3597,11 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3654,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3668,10 +3658,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45007</v>
+        <v>44937</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3683,13 +3673,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3732,7 +3717,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3746,10 +3731,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44840</v>
+        <v>44599</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3761,8 +3746,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3805,7 +3795,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3819,10 +3809,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45019</v>
+        <v>44916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3836,11 +3826,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3883,7 +3873,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3893,14 +3883,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45379</v>
+        <v>46077</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3913,7 +3903,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3956,7 +3946,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3966,14 +3956,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44680</v>
+        <v>46079</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3986,7 +3976,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.7</v>
+        <v>5.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4029,7 +4019,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4039,14 +4029,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45537</v>
+        <v>46079</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4058,13 +4048,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4107,7 +4092,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4117,14 +4102,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44599</v>
+        <v>46079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,13 +4121,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4185,7 +4165,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4195,14 +4175,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44916</v>
+        <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4214,13 +4194,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4263,7 +4238,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4277,10 +4252,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45553</v>
+        <v>45007</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4292,8 +4267,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4336,7 +4316,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4350,10 +4330,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45007</v>
+        <v>45933</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4365,13 +4345,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4414,7 +4389,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4428,10 +4403,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44937</v>
+        <v>45027</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4443,8 +4418,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>7.1</v>
+        <v>4.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4487,7 +4467,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4501,10 +4481,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45344</v>
+        <v>46090</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4517,7 +4497,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4560,7 +4540,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4574,10 +4554,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45370</v>
+        <v>45344</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4590,7 +4570,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>9.5</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4633,7 +4613,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4647,10 +4627,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44937</v>
+        <v>45968</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4662,8 +4642,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4706,7 +4691,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4720,10 +4705,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45027</v>
+        <v>45968</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4741,7 +4726,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4784,7 +4769,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4794,14 +4779,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45593</v>
+        <v>44599</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4814,7 +4799,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4857,7 +4842,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4871,10 +4856,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45373</v>
+        <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4888,11 +4873,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4935,7 +4920,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4949,10 +4934,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45373</v>
+        <v>45979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4964,8 +4949,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5008,7 +4998,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5022,10 +5012,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45527</v>
+        <v>45979</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5037,8 +5027,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5081,7 +5076,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5095,10 +5090,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44840</v>
+        <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5111,7 +5106,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5154,7 +5149,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5164,14 +5159,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45537</v>
+        <v>45832</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5183,13 +5178,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5232,7 +5222,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5242,14 +5232,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45537</v>
+        <v>45988</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5263,11 +5253,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5310,7 +5300,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5320,14 +5310,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45736</v>
+        <v>45007</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5339,8 +5329,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5383,7 +5378,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5397,10 +5392,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45280</v>
+        <v>46139</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5413,7 +5408,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5456,7 +5451,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5470,10 +5465,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45373</v>
+        <v>44916</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5487,11 +5482,11 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5534,7 +5529,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5548,10 +5543,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44756</v>
+        <v>45379</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5564,7 +5559,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5607,7 +5602,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5621,10 +5616,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45527</v>
+        <v>46079</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5637,7 +5632,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>5.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5680,7 +5675,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5694,10 +5689,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45968</v>
+        <v>45373</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5709,13 +5704,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5758,7 +5748,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5772,10 +5762,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45968</v>
+        <v>45553</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5787,13 +5777,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5836,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5846,14 +5831,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45979</v>
+        <v>45736</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5865,13 +5850,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5914,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5928,10 +5908,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45979</v>
+        <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5943,13 +5923,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5992,7 +5967,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6006,10 +5981,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45979</v>
+        <v>45280</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6021,13 +5996,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6070,7 +6040,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6084,10 +6054,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45933</v>
+        <v>46273</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6100,7 +6070,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>4.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6143,7 +6113,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6157,10 +6127,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45988</v>
+        <v>44840</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6172,13 +6142,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6221,7 +6186,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6235,10 +6200,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46041</v>
+        <v>44680</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6251,7 +6216,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.3</v>
+        <v>7.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6294,7 +6259,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6308,10 +6273,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46041</v>
+        <v>45016</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6323,8 +6288,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6367,7 +6337,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6381,10 +6351,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46077</v>
+        <v>45537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6396,8 +6366,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>0.8</v>
+        <v>6.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6440,7 +6415,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6454,10 +6429,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46079</v>
+        <v>45007</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6469,8 +6444,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6513,7 +6493,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6523,14 +6503,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46079</v>
+        <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6542,8 +6522,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6586,7 +6571,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6596,14 +6581,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46079</v>
+        <v>45373</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6615,8 +6600,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6659,7 +6649,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6669,14 +6659,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46079</v>
+        <v>44937</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6689,7 +6679,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6732,7 +6722,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6746,10 +6736,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46090</v>
+        <v>45019</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6761,8 +6751,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>5.1</v>
+        <v>0.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6805,7 +6800,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6815,14 +6810,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46139</v>
+        <v>45537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6834,8 +6829,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45835</v>
+        <v>45370</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45832</v>
+        <v>44756</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46079</v>
+        <v>45527</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.6</v>
+        <v>0.4</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7107,14 +7107,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46273</v>
+        <v>45593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45370</v>
+        <v>46077</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,19 +1859,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,46 +1899,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1948,14 +1944,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46077</v>
+        <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1967,8 +1963,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1977,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1995,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2008,42 +2009,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2057,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45979</v>
+        <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2074,11 +2075,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2118,35 +2119,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
@@ -2170,7 +2171,7 @@
         <v>44986</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2264,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2277,10 +2278,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45244</v>
+        <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2292,23 +2293,18 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2322,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2334,50 +2330,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2383,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46220</v>
+        <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2407,10 +2399,10 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.6</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2447,42 +2439,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2496,10 +2492,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44889</v>
+        <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2513,20 +2509,20 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2541,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2553,39 +2549,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45527</v>
+        <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3298,8 +3298,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3342,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3356,10 +3361,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46041</v>
+        <v>45007</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3371,8 +3376,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3415,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3429,10 +3439,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46041</v>
+        <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3445,7 +3455,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6.3</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3488,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3498,14 +3508,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45537</v>
+        <v>44840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3517,13 +3527,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3566,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3576,14 +3581,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45537</v>
+        <v>46041</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3595,13 +3600,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44937</v>
+        <v>46041</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7.1</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44599</v>
+        <v>45527</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3746,13 +3746,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3795,7 +3790,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3809,10 +3804,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44916</v>
+        <v>45933</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3824,13 +3819,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3890,7 +3880,7 @@
         <v>46077</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3946,7 +3936,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,14 +3946,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
         <v>46079</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3976,7 +3966,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4019,7 +4009,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4029,14 +4019,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
         <v>46079</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4049,7 +4039,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4109,7 +4099,7 @@
         <v>46079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4165,7 +4155,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4182,7 +4172,7 @@
         <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4195,7 +4185,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>5.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4238,7 +4228,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4252,10 +4242,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45007</v>
+        <v>46090</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4267,13 +4257,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4316,7 +4301,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4330,10 +4315,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45933</v>
+        <v>45968</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4345,8 +4330,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4389,7 +4379,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4403,10 +4393,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45027</v>
+        <v>45968</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4424,7 +4414,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4467,7 +4457,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4481,10 +4471,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46090</v>
+        <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4496,8 +4486,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4540,7 +4535,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4554,10 +4549,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45344</v>
+        <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4569,8 +4564,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4613,7 +4613,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45968</v>
+        <v>44840</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4642,13 +4642,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4691,7 +4686,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4705,10 +4700,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45968</v>
+        <v>45019</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4726,7 +4721,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4769,7 +4764,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4783,10 +4778,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44599</v>
+        <v>45379</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4799,7 +4794,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4842,7 +4837,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4859,7 +4854,7 @@
         <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4920,7 +4915,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4934,10 +4929,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45979</v>
+        <v>44680</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4949,13 +4944,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>7.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4998,7 +4988,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5012,10 +5002,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45979</v>
+        <v>45988</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5029,11 +5019,11 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5076,7 +5066,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5090,10 +5080,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45835</v>
+        <v>46139</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5106,7 +5096,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5149,7 +5139,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5163,10 +5153,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45832</v>
+        <v>45835</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5179,7 +5169,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5222,7 +5212,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5236,10 +5226,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45988</v>
+        <v>45832</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5251,13 +5241,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5300,7 +5285,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5310,14 +5295,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5331,11 +5316,11 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5378,7 +5363,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5388,14 +5373,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46139</v>
+        <v>45537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5407,8 +5392,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5451,7 +5441,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5465,10 +5455,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44916</v>
+        <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5480,13 +5470,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>5.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5529,7 +5514,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5543,10 +5528,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45379</v>
+        <v>45373</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5558,8 +5543,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5592,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5616,10 +5606,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46079</v>
+        <v>44756</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5632,7 +5622,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5675,7 +5665,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5689,10 +5679,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45373</v>
+        <v>45527</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5705,7 +5695,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4.2</v>
+        <v>0.4</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5748,7 +5738,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5762,10 +5752,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45553</v>
+        <v>44916</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5777,8 +5767,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5816,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5831,14 +5826,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45736</v>
+        <v>45007</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,8 +5845,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44840</v>
+        <v>44599</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5923,8 +5923,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5967,7 +5972,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5981,10 +5986,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45280</v>
+        <v>44916</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5996,8 +6001,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6040,7 +6050,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6054,10 +6064,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46273</v>
+        <v>45553</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6070,7 +6080,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6113,7 +6123,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6127,10 +6137,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44840</v>
+        <v>44937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6143,7 +6153,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6186,7 +6196,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6200,10 +6210,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44680</v>
+        <v>45344</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6216,7 +6226,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6259,7 +6269,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6273,10 +6283,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45016</v>
+        <v>45370</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6288,13 +6298,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>9.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6337,7 +6342,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6347,14 +6352,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45537</v>
+        <v>45027</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6368,11 +6373,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6415,7 +6420,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6429,10 +6434,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45007</v>
+        <v>46273</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6444,13 +6449,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6493,7 +6493,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6510,7 +6510,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6588,7 +6588,7 @@
         <v>45373</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6600,13 +6600,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6649,7 +6644,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6659,14 +6654,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44937</v>
+        <v>45736</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6679,7 +6674,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6722,7 +6717,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6736,10 +6731,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45019</v>
+        <v>45280</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6751,13 +6746,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6800,7 +6790,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6810,14 +6800,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45537</v>
+        <v>45016</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6831,11 +6821,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6868,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6888,14 +6878,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45370</v>
+        <v>45537</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6907,8 +6897,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6946,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6960,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44756</v>
+        <v>45007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6980,8 +6975,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I78" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45527</v>
+        <v>44937</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>45593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>46077</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>44986</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45007</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>46041</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>46041</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45527</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45933</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>46077</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>46079</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>46079</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>46079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>46090</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45968</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45968</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>44840</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45019</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45379</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44680</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>45988</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>46139</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45835</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>45832</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>45537</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45373</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>44756</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45527</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>44916</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>45007</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44599</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44916</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>45553</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>44937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45344</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45370</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45027</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>46273</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45373</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45736</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45280</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45016</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>45537</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>44937</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>46077</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>44986</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45007</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>46041</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>46041</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>45527</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3807,7 +3807,7 @@
         <v>45933</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>46077</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>46079</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>46079</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         <v>46079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4172,7 +4172,7 @@
         <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4245,7 +4245,7 @@
         <v>46090</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
         <v>45968</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45968</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         <v>44840</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45019</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45379</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         <v>44680</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         <v>45988</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>46139</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45835</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5229,7 +5229,7 @@
         <v>45832</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>45537</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>45537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
         <v>45373</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>44756</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5682,7 +5682,7 @@
         <v>45527</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
         <v>44916</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>45007</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44599</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>44916</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>45553</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>44937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45344</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45370</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>45027</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>46273</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45373</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45736</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>45280</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45016</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>45537</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>44937</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45593</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46077</v>
+        <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,19 +1859,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,42 +1899,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1944,14 +1948,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45979</v>
+        <v>44986</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1965,20 +1969,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1993,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2005,46 +2009,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2054,14 +2058,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44889</v>
+        <v>46077</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2073,13 +2077,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2088,10 +2087,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2106,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2119,42 +2118,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2164,14 +2163,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44986</v>
+        <v>45979</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2185,21 +2184,21 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>9.4</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2213,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2225,46 +2224,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2278,10 +2277,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46220</v>
+        <v>45244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2293,17 +2292,22 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2318,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2330,46 +2334,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2383,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45370</v>
+        <v>44889</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2398,11 +2406,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2439,46 +2452,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2492,10 +2501,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45244</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2507,23 +2516,18 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2537,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2549,43 +2553,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 29943-2022</t>
+          <t>A 25851-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44756</v>
+        <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>11.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 25851-2022</t>
+          <t>A 29943-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2899,14 +2899,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44733</v>
+        <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3286,7 +3286,7 @@
         <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3357,14 +3357,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,11 +3378,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44599</v>
+        <v>44937</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44840</v>
+        <v>44599</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3527,8 +3527,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3571,7 +3576,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3588,7 +3593,7 @@
         <v>46041</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3601,7 +3606,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>6.3</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3649,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3658,10 +3663,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46041</v>
+        <v>44916</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3673,8 +3678,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3717,7 +3727,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3731,10 +3741,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45527</v>
+        <v>46041</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3747,7 +3757,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>6.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3790,7 +3800,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3804,10 +3814,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45933</v>
+        <v>45007</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3819,8 +3829,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3863,7 +3878,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3873,14 +3888,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46077</v>
+        <v>45027</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3892,8 +3907,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3936,7 +3956,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3950,10 +3970,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46079</v>
+        <v>45344</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3966,7 +3986,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4009,7 +4029,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4019,14 +4039,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46079</v>
+        <v>44599</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4039,7 +4059,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4082,7 +4102,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4092,14 +4112,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46079</v>
+        <v>45933</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4112,7 +4132,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4155,7 +4175,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4169,10 +4189,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46079</v>
+        <v>46077</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4185,7 +4205,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.2</v>
+        <v>0.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4228,7 +4248,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4238,14 +4258,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46090</v>
+        <v>46079</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4258,7 +4278,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4301,7 +4321,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4315,10 +4335,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45968</v>
+        <v>46079</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4330,13 +4350,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4379,7 +4394,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4389,14 +4404,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45968</v>
+        <v>46079</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4408,13 +4423,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4457,7 +4467,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4467,14 +4477,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45979</v>
+        <v>46079</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4486,13 +4496,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4535,7 +4540,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4549,10 +4554,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45979</v>
+        <v>46090</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4564,13 +4569,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4613,7 +4613,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4627,10 +4627,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44840</v>
+        <v>45968</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4642,8 +4642,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4686,7 +4691,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4700,10 +4705,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45019</v>
+        <v>45968</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4721,7 +4726,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4764,7 +4769,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4778,10 +4783,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45379</v>
+        <v>45979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4793,8 +4798,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4837,7 +4847,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4854,7 +4864,7 @@
         <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4872,7 +4882,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4915,7 +4925,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4929,10 +4939,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44680</v>
+        <v>45979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4944,8 +4954,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4988,7 +5003,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5002,10 +5017,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45988</v>
+        <v>45007</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5023,7 +5038,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5066,7 +5081,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5080,10 +5095,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46139</v>
+        <v>45988</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5095,8 +5110,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5156,7 +5176,7 @@
         <v>45835</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5229,7 +5249,7 @@
         <v>45832</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5285,7 +5305,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5295,14 +5315,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45537</v>
+        <v>44916</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5320,7 +5340,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5363,7 +5383,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5373,14 +5393,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45537</v>
+        <v>45379</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5392,13 +5412,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5441,7 +5456,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5455,10 +5470,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46079</v>
+        <v>45373</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5471,7 +5486,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5514,7 +5529,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5528,10 +5543,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45373</v>
+        <v>46139</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5543,13 +5558,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5592,7 +5602,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5606,10 +5616,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44756</v>
+        <v>45553</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5622,7 +5632,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5665,7 +5675,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5679,10 +5689,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45527</v>
+        <v>46079</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5695,7 +5705,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.4</v>
+        <v>5.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5738,7 +5748,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5748,14 +5758,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44916</v>
+        <v>45736</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5767,13 +5777,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5816,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5830,10 +5835,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45007</v>
+        <v>44840</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5845,13 +5850,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44599</v>
+        <v>45280</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5923,13 +5923,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5972,7 +5967,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5986,10 +5981,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44916</v>
+        <v>44840</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6001,13 +5996,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6050,7 +6040,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6064,10 +6054,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45553</v>
+        <v>44680</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6080,7 +6070,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>7.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6123,7 +6113,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6137,10 +6127,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44937</v>
+        <v>46273</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6153,7 +6143,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6196,7 +6186,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6210,10 +6200,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45344</v>
+        <v>45016</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6225,8 +6215,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6269,7 +6264,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6279,14 +6274,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45370</v>
+        <v>45537</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6298,8 +6293,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45027</v>
+        <v>45007</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6434,10 +6434,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46273</v>
+        <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6449,8 +6449,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6510,7 +6515,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6571,7 +6576,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6585,10 +6590,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45373</v>
+        <v>44937</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6601,7 +6606,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6644,7 +6649,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6654,14 +6659,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45736</v>
+        <v>45019</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6673,8 +6678,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6717,7 +6727,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6727,14 +6737,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45280</v>
+        <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6746,8 +6756,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6790,7 +6805,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6804,10 +6819,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45016</v>
+        <v>45370</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6819,13 +6834,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>9.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6868,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6878,14 +6888,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45537</v>
+        <v>44756</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6897,13 +6907,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6946,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6960,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45007</v>
+        <v>45527</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6975,13 +6980,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44937</v>
+        <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7107,14 +7107,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45593</v>
+        <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45370</v>
+        <v>46077</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,19 +1859,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,46 +1899,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1948,14 +1944,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44986</v>
+        <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1969,21 +1965,21 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>9.4</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1997,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2009,46 +2005,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,14 +2054,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46077</v>
+        <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2077,8 +2073,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2087,10 +2088,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2105,7 +2106,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,42 +2119,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2167,10 +2168,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45979</v>
+        <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2182,13 +2183,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2228,42 +2224,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2273,14 +2269,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45244</v>
+        <v>44986</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2294,11 +2290,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>9.4</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2338,46 +2334,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2383,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44889</v>
+        <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,16 +2398,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2452,42 +2439,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2501,10 +2492,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,17 +2507,22 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2541,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2553,39 +2549,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25851-2022</t>
+          <t>A 29943-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44733</v>
+        <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 29943-2022</t>
+          <t>A 25851-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2899,14 +2899,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44756</v>
+        <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>11.4</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3286,7 +3286,7 @@
         <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3357,14 +3357,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45537</v>
+        <v>45007</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,11 +3378,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44937</v>
+        <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44599</v>
+        <v>44840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3527,13 +3527,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3576,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3593,7 +3588,7 @@
         <v>46041</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3606,7 +3601,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.3</v>
+        <v>6.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3649,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3663,10 +3658,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44916</v>
+        <v>46041</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3678,13 +3673,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3727,7 +3717,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3737,14 +3727,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46041</v>
+        <v>46077</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3757,7 +3747,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3800,7 +3790,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3814,10 +3804,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45007</v>
+        <v>46079</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3829,13 +3819,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3878,7 +3863,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3888,14 +3873,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45027</v>
+        <v>46079</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3907,13 +3892,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3956,7 +3936,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3966,14 +3946,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45344</v>
+        <v>46079</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3986,7 +3966,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4029,7 +4009,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4039,14 +4019,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44599</v>
+        <v>46079</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4059,7 +4039,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4102,7 +4082,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4116,10 +4096,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45933</v>
+        <v>46090</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4132,7 +4112,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4175,7 +4155,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4185,14 +4165,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46077</v>
+        <v>45933</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4205,7 +4185,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4248,7 +4228,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4258,14 +4238,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46079</v>
+        <v>44840</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4278,7 +4258,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4321,7 +4301,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4335,10 +4315,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46079</v>
+        <v>45019</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4350,8 +4330,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4394,7 +4379,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4404,14 +4389,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46079</v>
+        <v>45379</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4424,7 +4409,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4467,7 +4452,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4477,14 +4462,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46079</v>
+        <v>44680</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4497,7 +4482,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4540,7 +4525,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4554,10 +4539,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46090</v>
+        <v>45968</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4569,8 +4554,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4630,7 +4620,7 @@
         <v>45968</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4691,7 +4681,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4705,10 +4695,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45968</v>
+        <v>46139</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4720,13 +4710,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4786,7 +4771,7 @@
         <v>45979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4864,7 +4849,7 @@
         <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4942,7 +4927,7 @@
         <v>45979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5003,7 +4988,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5017,10 +5002,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45007</v>
+        <v>45835</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5032,13 +5017,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5098,7 +5078,7 @@
         <v>45988</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5159,7 +5139,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5173,10 +5153,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45835</v>
+        <v>45832</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5189,7 +5169,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5232,7 +5212,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5246,10 +5226,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45832</v>
+        <v>46079</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5262,7 +5242,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5305,7 +5285,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5315,14 +5295,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44916</v>
+        <v>45537</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5340,7 +5320,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5383,7 +5363,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5393,14 +5373,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45379</v>
+        <v>45537</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5412,8 +5392,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5456,7 +5441,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5473,7 +5458,7 @@
         <v>45373</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5485,8 +5470,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>1.6</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5529,7 +5519,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5543,10 +5533,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46139</v>
+        <v>44756</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5559,7 +5549,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5592,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5616,10 +5606,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45553</v>
+        <v>45527</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5632,7 +5622,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>0.4</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5675,7 +5665,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5689,10 +5679,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46079</v>
+        <v>44916</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5704,8 +5694,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5748,7 +5743,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5758,14 +5753,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45736</v>
+        <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5777,8 +5772,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44840</v>
+        <v>46273</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45280</v>
+        <v>44599</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5923,8 +5923,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5967,7 +5972,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5981,10 +5986,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44840</v>
+        <v>44916</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5996,8 +6001,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6040,7 +6050,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6054,10 +6064,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44680</v>
+        <v>45553</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6070,7 +6080,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.7</v>
+        <v>5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6113,7 +6123,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6127,10 +6137,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46273</v>
+        <v>44937</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6143,7 +6153,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>7.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6186,7 +6196,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6200,10 +6210,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45016</v>
+        <v>45344</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6215,13 +6225,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6264,7 +6269,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6274,14 +6279,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45537</v>
+        <v>45370</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6293,13 +6298,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>6.6</v>
+        <v>9.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45007</v>
+        <v>45027</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>4.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6437,7 +6437,7 @@
         <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6515,7 +6515,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6527,13 +6527,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6576,7 +6571,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6586,14 +6581,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44937</v>
+        <v>45736</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6606,7 +6601,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6649,7 +6644,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6663,10 +6658,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45019</v>
+        <v>45280</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6678,13 +6673,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6727,7 +6717,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6737,14 +6727,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45537</v>
+        <v>45016</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6758,11 +6748,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6805,7 +6795,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6815,14 +6805,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45370</v>
+        <v>45537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6834,8 +6824,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6873,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6892,10 +6887,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44756</v>
+        <v>45007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6907,8 +6902,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45527</v>
+        <v>44937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7041,7 +7041,7 @@
         <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46077</v>
+        <v>45244</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,11 +1858,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1871,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1883,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1895,46 +1900,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1948,10 +1957,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45979</v>
+        <v>45370</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1963,16 +1972,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2009,42 +2013,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,10 +2066,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44889</v>
+        <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2075,11 +2083,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2119,42 +2127,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2164,14 +2172,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46220</v>
+        <v>44986</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2183,17 +2191,22 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2208,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2220,46 +2233,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2269,14 +2282,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44986</v>
+        <v>44889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2290,21 +2303,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2318,7 +2331,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2330,46 +2343,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2379,14 +2392,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45370</v>
+        <v>46077</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2399,19 +2412,19 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2426,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2439,46 +2452,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2492,10 +2501,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45244</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2507,23 +2516,18 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2537,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2549,43 +2553,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45537</v>
+        <v>45007</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3300,11 +3300,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45007</v>
+        <v>45527</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3376,13 +3376,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3420,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3435,14 +3430,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44599</v>
+        <v>45593</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3455,7 +3450,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3493,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3507,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44840</v>
+        <v>45527</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3528,7 +3523,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3571,7 +3566,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3585,10 +3580,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46041</v>
+        <v>44916</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3600,8 +3595,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>6.3</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46041</v>
+        <v>45379</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3727,14 +3727,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46077</v>
+        <v>45373</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3790,7 +3790,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3800,14 +3800,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46079</v>
+        <v>45537</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3819,8 +3819,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3863,7 +3868,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3877,10 +3882,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46079</v>
+        <v>45537</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3892,8 +3897,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3936,7 +3946,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3946,14 +3956,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46079</v>
+        <v>44937</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3966,7 +3976,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4009,7 +4019,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4019,14 +4029,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46079</v>
+        <v>45933</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4039,7 +4049,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4082,7 +4092,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4096,10 +4106,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46090</v>
+        <v>45553</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4112,7 +4122,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4155,7 +4165,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4169,10 +4179,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45933</v>
+        <v>44599</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4184,8 +4194,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4228,7 +4243,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4242,10 +4257,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44840</v>
+        <v>44916</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4257,8 +4272,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4301,7 +4321,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4315,10 +4335,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45019</v>
+        <v>45007</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4336,7 +4356,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4379,7 +4399,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4393,10 +4413,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45379</v>
+        <v>45027</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4408,8 +4428,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4452,7 +4477,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4466,10 +4491,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44680</v>
+        <v>45968</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4481,8 +4506,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>7.7</v>
+        <v>1.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4542,7 +4572,7 @@
         <v>45968</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4603,7 +4633,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4613,14 +4643,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45968</v>
+        <v>45736</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4632,13 +4662,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4681,7 +4706,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4695,10 +4720,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46139</v>
+        <v>45344</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4711,7 +4736,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4771,7 +4796,7 @@
         <v>45979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4849,7 +4874,7 @@
         <v>45979</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4927,7 +4952,7 @@
         <v>45979</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4988,7 +5013,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5002,10 +5027,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45835</v>
+        <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5018,7 +5043,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5078,7 +5103,7 @@
         <v>45988</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5139,7 +5164,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5153,10 +5178,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45832</v>
+        <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5169,7 +5194,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5229,7 +5254,7 @@
         <v>46079</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5285,7 +5310,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5295,14 +5320,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45537</v>
+        <v>44840</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5314,13 +5339,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5363,7 +5383,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5373,14 +5393,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45537</v>
+        <v>45280</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5392,13 +5412,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5441,7 +5456,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5455,10 +5470,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45373</v>
+        <v>46041</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5470,13 +5485,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5519,7 +5529,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5533,10 +5543,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44756</v>
+        <v>46041</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5549,7 +5559,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5592,7 +5602,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5606,10 +5616,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45527</v>
+        <v>44840</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5622,7 +5632,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5665,7 +5675,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5675,14 +5685,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44916</v>
+        <v>46077</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5694,13 +5704,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5743,7 +5748,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5753,14 +5758,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45007</v>
+        <v>46079</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5772,13 +5777,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46273</v>
+        <v>46079</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5904,14 +5904,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44599</v>
+        <v>46079</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5923,13 +5923,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5972,7 +5967,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5986,10 +5981,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44916</v>
+        <v>44680</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6001,13 +5996,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>1.2</v>
+        <v>7.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6050,7 +6040,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6060,14 +6050,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45553</v>
+        <v>46079</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6080,7 +6070,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6123,7 +6113,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6137,10 +6127,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44937</v>
+        <v>46090</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6153,7 +6143,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>7.1</v>
+        <v>5.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6196,7 +6186,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6210,10 +6200,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45344</v>
+        <v>45016</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6225,8 +6215,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6269,7 +6264,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6279,14 +6274,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45370</v>
+        <v>45537</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6298,8 +6293,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6342,7 +6342,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6356,10 +6356,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45027</v>
+        <v>45007</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6437,7 +6437,7 @@
         <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>8.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6515,7 +6515,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6527,8 +6527,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6571,7 +6576,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6581,14 +6586,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45736</v>
+        <v>44937</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6601,7 +6606,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6644,7 +6649,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6658,10 +6663,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45280</v>
+        <v>45835</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6674,7 +6679,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6717,7 +6722,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6731,10 +6736,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45016</v>
+        <v>45832</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6746,13 +6751,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6805,14 +6805,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45537</v>
+        <v>45019</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6826,11 +6826,11 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6.6</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6883,14 +6883,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6904,11 +6904,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44937</v>
+        <v>45370</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>9.5</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45593</v>
+        <v>44756</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>4.8</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45527</v>
+        <v>46273</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45244</v>
+        <v>44889</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>0.7</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1900,50 +1900,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1957,10 +1953,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45370</v>
+        <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1972,11 +1968,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2013,46 +2014,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2062,14 +2059,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45979</v>
+        <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2083,20 +2080,20 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2111,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2123,46 +2120,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2176,10 +2173,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44986</v>
+        <v>46077</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2191,26 +2188,21 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2221,10 +2213,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2233,46 +2225,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2286,10 +2278,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44889</v>
+        <v>45370</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2301,16 +2293,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2347,42 +2334,46 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2392,14 +2383,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46077</v>
+        <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2403,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2421,10 +2412,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2439,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2452,42 +2443,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2501,10 +2492,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,17 +2507,22 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2541,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2553,39 +2549,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3286,7 +3286,7 @@
         <v>45007</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45527</v>
+        <v>44599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45593</v>
+        <v>45537</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3449,8 +3449,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3493,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3507,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45527</v>
+        <v>44840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3523,7 +3528,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3566,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3580,10 +3585,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44916</v>
+        <v>46090</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3595,13 +3600,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45379</v>
+        <v>44840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45373</v>
+        <v>45019</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3746,8 +3746,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3790,7 +3795,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3800,14 +3805,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45537</v>
+        <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3819,13 +3824,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3868,7 +3868,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3878,14 +3878,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45537</v>
+        <v>44680</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3897,13 +3897,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3946,7 +3941,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3960,10 +3955,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44937</v>
+        <v>45933</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3976,7 +3971,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7.1</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4019,7 +4014,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4033,10 +4028,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45933</v>
+        <v>45968</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4048,8 +4043,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4092,7 +4092,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4106,10 +4106,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45553</v>
+        <v>45968</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4121,8 +4121,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4165,7 +4170,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4179,10 +4184,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44599</v>
+        <v>45979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4196,7 +4201,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -4243,7 +4248,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4257,10 +4262,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44916</v>
+        <v>45979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4278,7 +4283,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4321,7 +4326,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4335,10 +4340,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45007</v>
+        <v>45979</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4352,7 +4357,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4399,7 +4404,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4409,14 +4414,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45027</v>
+        <v>45537</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4430,11 +4435,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4477,7 +4482,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4487,14 +4492,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45968</v>
+        <v>45537</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4508,11 +4513,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4555,7 +4560,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4569,10 +4574,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45968</v>
+        <v>45988</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4590,7 +4595,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4633,7 +4638,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4643,14 +4648,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45736</v>
+        <v>46139</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4663,7 +4668,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4706,7 +4711,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4720,10 +4725,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45344</v>
+        <v>45835</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4736,7 +4741,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4779,7 +4784,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4793,10 +4798,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45979</v>
+        <v>45832</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4808,13 +4813,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4857,7 +4857,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45979</v>
+        <v>45373</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4888,11 +4888,11 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4935,7 +4935,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45979</v>
+        <v>44756</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4964,13 +4964,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.7</v>
+        <v>4.8</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5013,7 +5008,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5027,10 +5022,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46139</v>
+        <v>46041</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5043,7 +5038,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5086,7 +5081,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5100,10 +5095,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45988</v>
+        <v>46041</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5115,13 +5110,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5164,7 +5154,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5178,10 +5168,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44599</v>
+        <v>45527</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5194,7 +5184,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.7</v>
+        <v>0.4</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5237,7 +5227,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5251,10 +5241,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46079</v>
+        <v>44916</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5266,8 +5256,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5310,7 +5305,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5324,10 +5319,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44840</v>
+        <v>45007</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5339,8 +5334,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5383,7 +5383,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5393,14 +5393,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45280</v>
+        <v>46077</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46041</v>
+        <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5539,14 +5539,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46041</v>
+        <v>46079</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5602,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5612,14 +5612,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44840</v>
+        <v>46079</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2.8</v>
+        <v>5.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5675,7 +5675,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5748,7 +5748,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5758,14 +5758,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46079</v>
+        <v>44599</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5777,8 +5777,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5826,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5840,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46079</v>
+        <v>44916</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,8 +5855,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5904,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5904,14 +5914,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46079</v>
+        <v>45553</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5924,7 +5934,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5967,7 +5977,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5981,10 +5991,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44680</v>
+        <v>44937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5997,7 +6007,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6040,7 +6050,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6050,14 +6060,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46079</v>
+        <v>45344</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6070,7 +6080,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6113,7 +6123,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6127,10 +6137,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46090</v>
+        <v>45370</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6143,7 +6153,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>5.1</v>
+        <v>9.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6186,7 +6196,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6200,10 +6210,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45016</v>
+        <v>46079</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6215,13 +6225,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6264,7 +6269,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6274,14 +6279,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45537</v>
+        <v>45027</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6295,11 +6300,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6342,7 +6347,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6356,10 +6361,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45007</v>
+        <v>45373</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6373,11 +6378,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6420,7 +6425,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6437,7 +6442,7 @@
         <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6449,13 +6454,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6508,14 +6508,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45373</v>
+        <v>45736</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6527,13 +6527,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6576,7 +6571,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6590,10 +6585,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44937</v>
+        <v>45280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6606,7 +6601,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6649,7 +6644,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6663,10 +6658,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45835</v>
+        <v>45016</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6678,8 +6673,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6722,7 +6722,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6732,14 +6732,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45832</v>
+        <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6751,8 +6751,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6795,7 +6800,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6809,10 +6814,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45019</v>
+        <v>46273</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6824,13 +6829,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6873,7 +6873,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6883,14 +6883,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45537</v>
+        <v>45007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6904,11 +6904,11 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45370</v>
+        <v>44937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>9.5</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44756</v>
+        <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46273</v>
+        <v>45527</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44889</v>
+        <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,16 +1858,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1904,42 +1899,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1949,14 +1948,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45979</v>
+        <v>44986</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1970,20 +1969,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1998,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2010,46 +2009,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2059,14 +2058,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44986</v>
+        <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2080,21 +2079,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9.4</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2108,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2120,46 +2119,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2169,14 +2168,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46077</v>
+        <v>44889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2188,8 +2187,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2198,10 +2202,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2216,7 +2220,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2229,42 +2233,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2278,10 +2282,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45370</v>
+        <v>45244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2293,8 +2297,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2303,7 +2312,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2318,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2330,50 +2339,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2383,14 +2392,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46220</v>
+        <v>46077</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2403,7 +2412,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2412,10 +2421,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2430,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2443,42 +2452,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2492,10 +2501,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45244</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2507,23 +2516,18 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2537,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2549,43 +2553,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45007</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3347,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44599</v>
+        <v>45373</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3376,8 +3376,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3420,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3430,14 +3435,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45537</v>
+        <v>45373</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3451,11 +3456,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3503,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3517,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44840</v>
+        <v>44937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3528,7 +3533,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3571,7 +3576,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3585,10 +3590,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46090</v>
+        <v>44916</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3600,8 +3605,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3654,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3658,10 +3668,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44840</v>
+        <v>45019</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3673,8 +3683,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3717,7 +3732,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3727,14 +3742,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45019</v>
+        <v>45537</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3748,11 +3763,11 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3812,7 +3827,7 @@
         <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3868,7 +3883,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3882,10 +3897,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44680</v>
+        <v>45373</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3898,7 +3913,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.7</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3941,7 +3956,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3955,10 +3970,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45933</v>
+        <v>45370</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3971,7 +3986,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4014,7 +4029,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4028,10 +4043,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45968</v>
+        <v>44756</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4043,13 +4058,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4092,7 +4102,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4102,14 +4112,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45968</v>
+        <v>45537</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4123,11 +4133,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4170,7 +4180,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4180,14 +4190,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45979</v>
+        <v>45537</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4248,7 +4258,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4262,10 +4272,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45979</v>
+        <v>44937</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4277,13 +4287,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>0.5</v>
+        <v>7.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4326,7 +4331,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4340,10 +4345,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45979</v>
+        <v>45527</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4355,13 +4360,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4404,7 +4404,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4414,14 +4414,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45537</v>
+        <v>44599</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4435,11 +4435,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4496,10 +4496,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45537</v>
+        <v>45593</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4511,13 +4511,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4560,7 +4555,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4574,10 +4569,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45988</v>
+        <v>45553</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4589,13 +4584,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4638,7 +4628,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4652,10 +4642,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46139</v>
+        <v>44916</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4667,8 +4657,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4711,7 +4706,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4725,10 +4720,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45835</v>
+        <v>45007</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4740,8 +4735,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45832</v>
+        <v>45027</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4813,8 +4813,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4857,7 +4862,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4871,10 +4876,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45373</v>
+        <v>45527</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4886,13 +4891,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4935,7 +4935,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4949,10 +4949,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44756</v>
+        <v>45933</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.8</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5022,10 +5022,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46041</v>
+        <v>45344</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.3</v>
+        <v>0.9</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5081,7 +5081,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5091,14 +5091,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46041</v>
+        <v>45736</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5168,10 +5168,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45527</v>
+        <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.4</v>
+        <v>3.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5227,7 +5227,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5241,10 +5241,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44916</v>
+        <v>45968</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5258,11 +5258,11 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5305,7 +5305,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45007</v>
+        <v>44840</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5334,13 +5334,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5383,7 +5378,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5393,14 +5388,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46077</v>
+        <v>45968</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5412,8 +5407,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46079</v>
+        <v>45280</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>2.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5539,14 +5539,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46079</v>
+        <v>45979</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5558,8 +5558,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5607,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5612,14 +5617,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46079</v>
+        <v>45979</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5631,8 +5636,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>5.3</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5675,7 +5685,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5685,14 +5695,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46079</v>
+        <v>45979</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5704,8 +5714,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5748,7 +5763,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5762,10 +5777,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44599</v>
+        <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5783,7 +5798,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5826,7 +5841,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5840,10 +5855,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44916</v>
+        <v>45988</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5857,11 +5872,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5904,7 +5919,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5918,10 +5933,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45553</v>
+        <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5934,7 +5949,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5977,7 +5992,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5991,10 +6006,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44937</v>
+        <v>45835</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6007,7 +6022,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.1</v>
+        <v>3.5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6050,7 +6065,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6064,10 +6079,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45344</v>
+        <v>44680</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6080,7 +6095,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6123,7 +6138,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6137,10 +6152,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45370</v>
+        <v>45832</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6153,7 +6168,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9.5</v>
+        <v>3.1</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6196,7 +6211,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6210,10 +6225,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46079</v>
+        <v>46041</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6226,7 +6241,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6269,7 +6284,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6283,10 +6298,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45027</v>
+        <v>46041</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6298,13 +6313,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>4.6</v>
+        <v>6.3</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6347,7 +6357,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6361,10 +6371,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45373</v>
+        <v>45016</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6378,11 +6388,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8.199999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6425,7 +6435,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6435,14 +6445,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45373</v>
+        <v>45537</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6454,8 +6464,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6513,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6508,14 +6523,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45736</v>
+        <v>46139</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6528,7 +6543,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6571,7 +6586,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6581,14 +6596,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45280</v>
+        <v>46077</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6601,7 +6616,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6644,7 +6659,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6654,14 +6669,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45016</v>
+        <v>46079</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6673,13 +6688,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6722,7 +6732,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6732,14 +6742,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45537</v>
+        <v>46079</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6751,13 +6761,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6800,7 +6805,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6810,14 +6815,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46273</v>
+        <v>46079</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6830,7 +6835,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6873,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6883,14 +6888,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45007</v>
+        <v>46079</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6902,13 +6907,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44937</v>
+        <v>46090</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45593</v>
+        <v>46079</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45527</v>
+        <v>46273</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44986</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>44889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>45244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>46077</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45007</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45373</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>45373</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>44937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>44916</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>45019</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>45537</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>45373</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>45370</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44756</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45537</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>45537</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>44937</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>45527</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>44599</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45593</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45553</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>44916</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45007</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45027</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45527</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>45933</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45344</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45736</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>45968</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44840</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45968</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45280</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45979</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>45979</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>45979</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45988</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45835</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>44680</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>45832</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>46041</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>46041</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>45016</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>45537</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>46139</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>46077</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>46079</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>46079</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>46079</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>46079</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>46090</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>46079</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>46273</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>44986</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>44889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>45244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
         <v>46077</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44480</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44733</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>44489</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>44505</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         <v>44582</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>44599</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3286,7 +3286,7 @@
         <v>45007</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45373</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>45373</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>44937</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>44916</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>45019</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>45537</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>45379</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>45373</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>45370</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>44756</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45537</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
         <v>45537</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         <v>44937</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         <v>45527</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>44599</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>45593</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45553</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>44916</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45007</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45027</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45527</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>45933</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45344</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         <v>45736</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>45968</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
         <v>44840</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45968</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45280</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>45979</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>45979</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
         <v>45979</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>45988</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45835</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>44680</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>45832</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>46041</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>46041</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>45016</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>45537</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
         <v>46139</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>46077</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>46079</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>46079</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>46079</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>46079</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>46090</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>46079</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>46273</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45253</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>45714</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE82"/>
+  <dimension ref="A1:AE81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45370</v>
+        <v>45244</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,8 +1858,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1868,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1883,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1895,50 +1900,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1948,14 +1953,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44986</v>
+        <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1969,21 +1974,21 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>9.4</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1997,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2009,46 +2014,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2062,10 +2067,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45979</v>
+        <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2077,13 +2082,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>8.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2123,42 +2123,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2168,14 +2168,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44889</v>
+        <v>46077</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2187,13 +2187,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2202,10 +2197,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2220,7 +2215,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2233,42 +2228,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2282,10 +2277,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45244</v>
+        <v>44889</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2299,21 +2294,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>0.7</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2327,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2339,50 +2334,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2396,10 +2387,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46077</v>
+        <v>44986</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2411,11 +2402,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2424,7 +2420,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2436,10 +2432,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2448,46 +2444,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2501,10 +2497,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>45370</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2517,10 +2513,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>2.3</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2557,35 +2553,39 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 56315-2021</t>
+          <t>A 25851-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44480</v>
+        <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2833,7 +2833,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 25851-2022</t>
+          <t>A 58922-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44733</v>
+        <v>44489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2918,8 +2918,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2962,7 +2967,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58922-2021</t>
+          <t>A 63049-2021</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2976,10 +2981,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44489</v>
+        <v>44505</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2997,7 +3002,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3040,7 +3045,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 63049-2021</t>
+          <t>A 3134-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3054,10 +3059,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44505</v>
+        <v>44582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3071,11 +3076,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3118,7 +3123,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 3134-2022</t>
+          <t>A 6109-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3132,10 +3137,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44582</v>
+        <v>44599</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3147,13 +3152,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3196,7 +3196,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 6109-2022</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3206,14 +3206,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44599</v>
+        <v>45537</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3225,8 +3225,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3269,7 +3274,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3283,10 +3288,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45007</v>
+        <v>45016</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3304,7 +3309,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3352,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3357,14 +3362,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45373</v>
+        <v>45537</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,11 +3383,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>6.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3430,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3439,10 +3444,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45373</v>
+        <v>45007</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,11 +3461,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>8.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3503,7 +3508,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3517,10 +3522,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44937</v>
+        <v>44599</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3533,7 +3538,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.3</v>
+        <v>3.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3576,7 +3581,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3590,10 +3595,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44916</v>
+        <v>45933</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3605,13 +3610,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45019</v>
+        <v>45007</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3742,14 +3742,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45537</v>
+        <v>44937</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3759,11 +3759,6 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>TROSA</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -3810,7 +3805,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3820,14 +3815,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45379</v>
+        <v>45593</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3840,7 +3835,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3883,7 +3878,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3897,10 +3892,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45373</v>
+        <v>45968</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3912,8 +3907,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45370</v>
+        <v>45968</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3985,8 +3985,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>9.5</v>
+        <v>1.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4029,7 +4034,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4043,10 +4048,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44756</v>
+        <v>45979</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4058,8 +4063,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>4.8</v>
+        <v>0.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4102,7 +4112,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4112,14 +4122,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45537</v>
+        <v>45979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4137,7 +4147,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4180,7 +4190,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4190,14 +4200,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45537</v>
+        <v>45979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4258,7 +4268,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4272,10 +4282,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44937</v>
+        <v>45527</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4288,7 +4298,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4331,7 +4341,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4345,10 +4355,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45527</v>
+        <v>45988</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4360,8 +4370,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4404,7 +4419,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4418,10 +4433,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44599</v>
+        <v>46273</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4433,13 +4448,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4482,7 +4492,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4492,14 +4502,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45593</v>
+        <v>46041</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4512,7 +4522,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.2</v>
+        <v>6.3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4555,7 +4565,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4569,10 +4579,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45553</v>
+        <v>46041</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4585,7 +4595,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4628,7 +4638,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4638,14 +4648,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44916</v>
+        <v>46077</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4657,13 +4667,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4706,7 +4711,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4720,10 +4725,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45007</v>
+        <v>46079</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4735,13 +4740,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4794,14 +4794,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45027</v>
+        <v>46079</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4813,13 +4813,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>4.6</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4862,7 +4857,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4872,14 +4867,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45527</v>
+        <v>46079</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4892,7 +4887,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4935,7 +4930,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4945,14 +4940,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45933</v>
+        <v>46079</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4965,7 +4960,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5008,7 +5003,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5022,10 +5017,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45344</v>
+        <v>46090</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5038,7 +5033,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5081,7 +5076,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5091,14 +5086,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45736</v>
+        <v>44840</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5111,7 +5106,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5154,7 +5149,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5168,10 +5163,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44599</v>
+        <v>46139</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5184,7 +5179,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5227,7 +5222,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5241,10 +5236,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45968</v>
+        <v>45835</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5256,13 +5251,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5305,7 +5295,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5319,10 +5309,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44840</v>
+        <v>45832</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5335,7 +5325,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5378,7 +5368,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5392,10 +5382,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45968</v>
+        <v>44840</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5407,13 +5397,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5456,7 +5441,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5470,10 +5455,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45280</v>
+        <v>45019</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5485,8 +5470,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I58" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5529,7 +5519,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5543,10 +5533,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45979</v>
+        <v>45379</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5558,13 +5548,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5607,7 +5592,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5621,10 +5606,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45979</v>
+        <v>44680</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5636,13 +5621,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.5</v>
+        <v>7.7</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5685,7 +5665,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5699,10 +5679,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45979</v>
+        <v>46079</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5714,13 +5694,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5763,7 +5738,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5773,14 +5748,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5794,11 +5769,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5841,7 +5816,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5851,14 +5826,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45988</v>
+        <v>45537</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5872,11 +5847,11 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5919,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5933,10 +5908,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44840</v>
+        <v>45373</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5948,8 +5923,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5992,7 +5972,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6006,10 +5986,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45835</v>
+        <v>44756</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6022,7 +6002,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6065,7 +6045,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6079,10 +6059,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44680</v>
+        <v>45527</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6095,7 +6075,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.7</v>
+        <v>0.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6138,7 +6118,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6152,10 +6132,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45832</v>
+        <v>44916</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6167,8 +6147,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>3.1</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6211,7 +6196,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6225,10 +6210,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46041</v>
+        <v>45007</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6240,8 +6225,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6284,7 +6274,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6298,10 +6288,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46041</v>
+        <v>44599</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6313,8 +6303,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>6.3</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6357,7 +6352,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6371,10 +6366,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45016</v>
+        <v>44916</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6388,11 +6383,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6435,7 +6430,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6445,14 +6440,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45537</v>
+        <v>45553</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6464,13 +6459,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6513,7 +6503,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6527,10 +6517,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46139</v>
+        <v>44937</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6543,7 +6533,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6586,7 +6576,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6596,14 +6586,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46077</v>
+        <v>45344</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6616,7 +6606,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6659,7 +6649,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6669,14 +6659,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46079</v>
+        <v>45370</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6689,7 +6679,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>5.2</v>
+        <v>9.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6732,7 +6722,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6746,10 +6736,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46079</v>
+        <v>45027</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6761,8 +6751,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6805,7 +6800,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6815,14 +6810,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46079</v>
+        <v>45373</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6834,8 +6829,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6888,14 +6888,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46079</v>
+        <v>45373</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6961,14 +6961,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46090</v>
+        <v>45736</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46079</v>
+        <v>45280</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7097,24 +7097,24 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>S 4203-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46273</v>
+        <v>45253</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7167,10 +7167,10 @@
       </c>
       <c r="V80" s="2" t="inlineStr"/>
     </row>
-    <row r="81" ht="15" customHeight="1">
+    <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>S 4203-2023</t>
+          <t>S 632-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7180,14 +7180,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45253</v>
+        <v>45714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7199,8 +7199,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>3.6</v>
+        <v>36.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -7239,84 +7244,6 @@
         <v>0</v>
       </c>
       <c r="V81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>S 632-2025</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E82" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>TROSA</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45244</v>
+        <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,13 +1858,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1873,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1888,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1900,43 +1895,43 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
@@ -1960,7 +1955,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2053,7 +2048,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2063,14 +2058,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46220</v>
+        <v>46077</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2083,7 +2078,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2092,10 +2087,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2110,7 +2105,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2123,42 +2118,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2172,10 +2167,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46077</v>
+        <v>44986</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2187,11 +2182,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>9.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2212,10 +2212,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2224,46 +2224,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44889</v>
+        <v>45244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2294,20 +2294,20 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>0.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2322,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2334,46 +2334,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2383,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44986</v>
+        <v>44889</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2404,21 +2408,21 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
@@ -2432,7 +2436,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2444,46 +2448,46 @@
         <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2497,10 +2501,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45370</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2513,10 +2517,10 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.3</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2553,39 +2557,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 25851-2022</t>
+          <t>A 29943-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2753,14 +2753,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44733</v>
+        <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2816,7 +2816,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 29943-2022</t>
+          <t>A 25851-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2826,14 +2826,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44756</v>
+        <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>11.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>44489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44505</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>44599</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3206,14 +3206,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45537</v>
+        <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3225,13 +3225,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3274,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3284,14 +3279,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45016</v>
+        <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,11 +3300,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3352,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3369,7 +3364,7 @@
         <v>45537</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3387,7 +3382,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>6.6</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3430,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3444,10 +3439,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45007</v>
+        <v>44937</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3459,13 +3454,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>7.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3508,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3525,7 +3515,7 @@
         <v>44599</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3537,8 +3527,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3581,7 +3576,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3595,10 +3590,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45933</v>
+        <v>44916</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3610,8 +3605,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3671,7 +3671,7 @@
         <v>45007</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3732,7 +3732,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3746,10 +3746,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44937</v>
+        <v>45933</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3805,7 +3805,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3815,14 +3815,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45593</v>
+        <v>45027</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3834,8 +3834,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3878,7 +3883,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3892,10 +3897,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45968</v>
+        <v>46041</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3907,13 +3912,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3956,7 +3956,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3970,10 +3970,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45968</v>
+        <v>46041</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3985,13 +3985,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4034,7 +4029,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4048,10 +4043,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45979</v>
+        <v>45344</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4063,13 +4058,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4112,7 +4102,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4126,10 +4116,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45979</v>
+        <v>45968</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4143,11 +4133,11 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4190,7 +4180,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4204,10 +4194,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45979</v>
+        <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4221,11 +4211,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4268,7 +4258,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4282,10 +4272,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45527</v>
+        <v>45979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4297,8 +4287,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4341,7 +4336,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4355,10 +4350,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45988</v>
+        <v>45979</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4372,11 +4367,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4419,7 +4414,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4433,10 +4428,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46273</v>
+        <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4448,8 +4443,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4506,10 +4506,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46041</v>
+        <v>45988</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4521,8 +4521,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>6.3</v>
+        <v>0.6</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4565,7 +4570,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4579,10 +4584,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46041</v>
+        <v>44599</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4595,7 +4600,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4655,7 +4660,7 @@
         <v>46077</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4711,7 +4716,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4721,14 +4726,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
         <v>46079</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4741,7 +4746,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4784,7 +4789,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4794,14 +4799,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
         <v>46079</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4814,7 +4819,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4874,7 +4879,7 @@
         <v>46079</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4930,7 +4935,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4947,7 +4952,7 @@
         <v>46079</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4960,7 +4965,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5020,7 +5025,7 @@
         <v>46090</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5076,7 +5081,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5090,10 +5095,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44840</v>
+        <v>45007</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5105,8 +5110,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5149,7 +5159,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5163,10 +5173,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46139</v>
+        <v>45835</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5179,7 +5189,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5222,7 +5232,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5236,10 +5246,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45835</v>
+        <v>45832</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5252,7 +5262,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5295,7 +5305,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5309,10 +5319,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45832</v>
+        <v>44916</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5324,8 +5334,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5368,7 +5383,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5382,10 +5397,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44840</v>
+        <v>45379</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5398,7 +5413,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5441,7 +5456,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5455,10 +5470,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45019</v>
+        <v>45373</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5470,13 +5485,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5519,7 +5529,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5533,10 +5543,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45379</v>
+        <v>46139</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5549,7 +5559,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3.4</v>
+        <v>1.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5592,7 +5602,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5606,10 +5616,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44680</v>
+        <v>45553</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5622,7 +5632,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7.7</v>
+        <v>5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5682,7 +5692,7 @@
         <v>46079</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5738,7 +5748,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5752,10 +5762,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45537</v>
+        <v>45736</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5767,13 +5777,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5816,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5826,14 +5831,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45537</v>
+        <v>44840</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5845,13 +5850,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5908,10 +5908,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45373</v>
+        <v>45280</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5923,13 +5923,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5972,7 +5967,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5986,10 +5981,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44756</v>
+        <v>44840</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6002,7 +5997,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6045,7 +6040,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6059,10 +6054,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45527</v>
+        <v>44680</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6075,7 +6070,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.4</v>
+        <v>7.7</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6118,7 +6113,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6132,10 +6127,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44916</v>
+        <v>46273</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6147,13 +6142,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>4.4</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6196,7 +6186,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6210,10 +6200,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45007</v>
+        <v>45016</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6231,7 +6221,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6274,7 +6264,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6284,14 +6274,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44599</v>
+        <v>45537</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6305,11 +6295,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6352,7 +6342,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6366,10 +6356,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44916</v>
+        <v>45007</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6383,11 +6373,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6430,7 +6420,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6444,10 +6434,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45553</v>
+        <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6459,8 +6449,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6503,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6517,10 +6512,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44937</v>
+        <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6532,8 +6527,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6576,7 +6576,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45344</v>
+        <v>44937</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6649,7 +6649,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6663,10 +6663,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45370</v>
+        <v>45019</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6678,8 +6678,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>9.5</v>
+        <v>0.5</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6722,7 +6727,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6732,14 +6737,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45027</v>
+        <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6753,11 +6758,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4.6</v>
+        <v>1.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6800,7 +6805,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6814,10 +6819,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45373</v>
+        <v>45370</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6829,13 +6834,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45373</v>
+        <v>44756</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6961,14 +6961,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45736</v>
+        <v>45527</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45280</v>
+        <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>45253</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45370</v>
+        <v>44889</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,11 +1858,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1899,46 +1904,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1948,14 +1949,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45979</v>
+        <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1967,13 +1968,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1982,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>1</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2000,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2013,42 +2009,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,14 +2054,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46077</v>
+        <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2077,8 +2073,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2087,10 +2088,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2105,7 +2106,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2118,35 +2119,35 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
@@ -2170,7 +2171,7 @@
         <v>44986</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2263,7 +2264,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2277,10 +2278,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45244</v>
+        <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2292,23 +2293,18 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
         <v>0</v>
       </c>
@@ -2322,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2334,50 +2330,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2383,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44889</v>
+        <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,16 +2398,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2452,42 +2439,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2501,10 +2492,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,17 +2507,22 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2541,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2553,39 +2549,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44505</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>44599</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3286,7 +3286,7 @@
         <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3357,14 +3357,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45537</v>
+        <v>45007</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,11 +3378,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44937</v>
+        <v>44599</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3508,14 +3508,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44599</v>
+        <v>45537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3529,11 +3529,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3576,7 +3576,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3586,14 +3586,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44916</v>
+        <v>45537</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3654,7 +3654,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45007</v>
+        <v>44840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3683,13 +3683,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3749,7 +3744,7 @@
         <v>45933</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3805,7 +3800,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3815,14 +3810,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45027</v>
+        <v>46077</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3834,13 +3829,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>4.6</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3883,7 +3873,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3897,10 +3887,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46041</v>
+        <v>46079</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3913,7 +3903,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3956,7 +3946,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3966,14 +3956,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46041</v>
+        <v>46079</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3986,7 +3976,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>6.3</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4029,7 +4019,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4039,14 +4029,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45344</v>
+        <v>46079</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4059,7 +4049,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4102,7 +4092,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4112,14 +4102,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45968</v>
+        <v>46079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4131,13 +4121,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4180,7 +4165,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4194,10 +4179,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45968</v>
+        <v>46090</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4209,13 +4194,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4258,7 +4238,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4272,10 +4252,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45979</v>
+        <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4289,11 +4269,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4336,7 +4316,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4350,10 +4330,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45979</v>
+        <v>45968</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4367,11 +4347,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4414,7 +4394,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4431,7 +4411,7 @@
         <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4492,7 +4472,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4506,10 +4486,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45988</v>
+        <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4523,11 +4503,11 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4570,7 +4550,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4584,10 +4564,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44599</v>
+        <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4599,8 +4579,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4643,7 +4628,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4653,14 +4638,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46077</v>
+        <v>45988</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4672,8 +4657,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4716,7 +4706,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4726,14 +4716,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46079</v>
+        <v>44840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4746,7 +4736,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4789,7 +4779,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4803,10 +4793,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46079</v>
+        <v>45019</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4818,8 +4808,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4862,7 +4857,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4872,14 +4867,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46079</v>
+        <v>45379</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4892,7 +4887,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5.3</v>
+        <v>3.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4935,7 +4930,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4945,14 +4940,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46079</v>
+        <v>44680</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4965,7 +4960,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.7</v>
+        <v>7.7</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5008,7 +5003,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5022,10 +5017,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46090</v>
+        <v>46139</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5038,7 +5033,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5081,7 +5076,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5095,10 +5090,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45007</v>
+        <v>45835</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5110,13 +5105,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5159,7 +5149,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5173,10 +5163,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45835</v>
+        <v>45832</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5189,7 +5179,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5232,7 +5222,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5246,10 +5236,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45832</v>
+        <v>46041</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5262,7 +5252,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5305,7 +5295,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5319,10 +5309,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44916</v>
+        <v>46041</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5334,13 +5324,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>1.2</v>
+        <v>3.3</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5383,7 +5368,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5397,10 +5382,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45379</v>
+        <v>45373</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5412,8 +5397,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5456,7 +5446,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5470,10 +5460,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45373</v>
+        <v>44756</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5486,7 +5476,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5529,7 +5519,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5543,10 +5533,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46139</v>
+        <v>45527</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5559,7 +5549,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5592,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5616,10 +5606,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45553</v>
+        <v>44916</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5631,8 +5621,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5692,7 +5687,7 @@
         <v>46079</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5748,7 +5743,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5758,14 +5753,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45736</v>
+        <v>45007</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5777,8 +5772,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44840</v>
+        <v>44599</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,8 +5850,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5899,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5908,10 +5913,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45280</v>
+        <v>44916</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5923,8 +5928,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5967,7 +5977,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5981,10 +5991,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44840</v>
+        <v>45553</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5997,7 +6007,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6040,7 +6050,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6054,10 +6064,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44680</v>
+        <v>44937</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6070,7 +6080,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6113,7 +6123,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6127,10 +6137,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46273</v>
+        <v>45344</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6143,7 +6153,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6186,7 +6196,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6200,10 +6210,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45016</v>
+        <v>45370</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6215,13 +6225,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.6</v>
+        <v>9.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6264,7 +6269,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6274,14 +6279,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45537</v>
+        <v>45027</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6295,11 +6300,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6342,7 +6347,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6356,10 +6361,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45007</v>
+        <v>45373</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6373,11 +6378,11 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6420,7 +6425,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6437,7 +6442,7 @@
         <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6449,13 +6454,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6512,10 +6512,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45373</v>
+        <v>46273</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6527,13 +6527,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6576,7 +6571,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6586,14 +6581,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44937</v>
+        <v>45736</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6606,7 +6601,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6649,7 +6644,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6663,10 +6658,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45019</v>
+        <v>45280</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6678,13 +6673,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>0.5</v>
+        <v>2.7</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6727,7 +6717,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6737,14 +6727,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45537</v>
+        <v>45016</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6758,11 +6748,11 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6805,7 +6795,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6815,14 +6805,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45370</v>
+        <v>45537</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6834,8 +6824,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6873,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6892,10 +6887,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44756</v>
+        <v>45007</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6907,8 +6902,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45527</v>
+        <v>44937</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7041,7 +7041,7 @@
         <v>45593</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45253</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44889</v>
+        <v>45244</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1860,20 +1860,20 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>0.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1900,46 +1900,50 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1949,14 +1953,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46077</v>
+        <v>45370</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1969,19 +1973,19 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1996,7 +2000,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2009,42 +2013,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2054,14 +2062,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45979</v>
+        <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2075,20 +2083,20 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2103,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2115,46 +2123,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2164,14 +2172,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44986</v>
+        <v>44889</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2185,21 +2193,21 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
@@ -2213,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2225,39 +2233,39 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
@@ -2281,7 +2289,7 @@
         <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2369,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2383,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45370</v>
+        <v>45979</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2398,11 +2406,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2439,46 +2452,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2488,14 +2497,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45244</v>
+        <v>46077</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2507,26 +2516,21 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
@@ -2537,10 +2541,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2549,43 +2553,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44505</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>44599</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3210,10 +3210,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45527</v>
+        <v>45007</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3225,8 +3225,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3269,7 +3274,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3279,14 +3284,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45537</v>
+        <v>44916</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3304,7 +3309,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3352,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3361,10 +3366,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45007</v>
+        <v>45379</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3376,13 +3381,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44599</v>
+        <v>45373</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3515,7 +3515,7 @@
         <v>45537</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45537</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44840</v>
+        <v>44937</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.9</v>
+        <v>7.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3727,7 +3727,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45933</v>
+        <v>44599</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3756,8 +3756,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3800,7 +3805,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3810,14 +3815,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46077</v>
+        <v>44916</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3829,8 +3834,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3873,7 +3883,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3887,10 +3897,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46079</v>
+        <v>45553</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3903,7 +3913,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3946,7 +3956,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3956,14 +3966,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46079</v>
+        <v>45007</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3975,8 +3985,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4019,7 +4034,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4029,14 +4044,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46079</v>
+        <v>45027</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4048,8 +4063,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4092,7 +4112,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4102,14 +4122,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46079</v>
+        <v>45344</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4122,7 +4142,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4165,7 +4185,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4179,10 +4199,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46090</v>
+        <v>45835</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4195,7 +4215,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4238,7 +4258,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4252,10 +4272,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45968</v>
+        <v>45832</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4267,13 +4287,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4316,7 +4331,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4326,14 +4341,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45968</v>
+        <v>45736</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4345,13 +4360,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4394,7 +4404,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4408,10 +4418,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45979</v>
+        <v>44599</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4423,13 +4433,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4472,7 +4477,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4486,10 +4491,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45979</v>
+        <v>46139</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4501,13 +4506,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4564,10 +4564,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45979</v>
+        <v>44840</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4579,13 +4579,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4628,7 +4623,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4642,10 +4637,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45988</v>
+        <v>45280</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4657,13 +4652,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4706,7 +4696,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4720,10 +4710,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44840</v>
+        <v>46079</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4736,7 +4726,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4779,7 +4769,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4793,10 +4783,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45019</v>
+        <v>45933</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4808,13 +4798,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4857,7 +4842,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4871,10 +4856,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45379</v>
+        <v>44840</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4887,7 +4872,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4947,7 +4932,7 @@
         <v>44680</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5003,7 +4988,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5017,10 +5002,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46139</v>
+        <v>45016</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5032,8 +5017,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5076,7 +5066,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5086,14 +5076,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45835</v>
+        <v>45537</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5105,8 +5095,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5149,7 +5144,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5163,10 +5158,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45832</v>
+        <v>45007</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5178,8 +5173,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46041</v>
+        <v>45373</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5251,8 +5251,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>6.3</v>
+        <v>1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5295,7 +5300,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5309,10 +5314,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46041</v>
+        <v>45373</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5324,8 +5329,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>3.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5368,7 +5378,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5382,10 +5392,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45373</v>
+        <v>44937</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5397,13 +5407,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5446,7 +5451,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5460,10 +5465,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44756</v>
+        <v>46273</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5476,7 +5481,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5519,7 +5524,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5533,10 +5538,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45527</v>
+        <v>45019</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5548,8 +5553,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5592,7 +5602,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5606,10 +5616,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44916</v>
+        <v>45968</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5623,11 +5633,11 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5670,7 +5680,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5680,14 +5690,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46079</v>
+        <v>45537</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5699,8 +5709,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>5.6</v>
+        <v>1.3</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5743,7 +5758,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5757,10 +5772,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45007</v>
+        <v>45968</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5778,7 +5793,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5836,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5850,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44599</v>
+        <v>45370</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,13 +5865,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.7</v>
+        <v>9.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5899,7 +5909,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5913,10 +5923,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44916</v>
+        <v>44756</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5928,13 +5938,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>4.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5977,7 +5982,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5991,10 +5996,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45553</v>
+        <v>45979</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6006,8 +6011,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6050,7 +6060,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6064,10 +6074,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44937</v>
+        <v>45979</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6079,8 +6089,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6123,7 +6138,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6137,10 +6152,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45344</v>
+        <v>45979</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6152,8 +6167,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6196,7 +6216,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6210,10 +6230,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45370</v>
+        <v>45527</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6226,7 +6246,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>9.5</v>
+        <v>0.4</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6269,7 +6289,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6283,10 +6303,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45027</v>
+        <v>45988</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6304,7 +6324,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6347,7 +6367,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6357,14 +6377,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45373</v>
+        <v>45593</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6376,13 +6396,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>8.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6425,7 +6440,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6439,10 +6454,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45373</v>
+        <v>45527</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6455,7 +6470,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6513,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6512,10 +6527,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46273</v>
+        <v>46041</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6528,7 +6543,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6571,7 +6586,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6581,14 +6596,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45736</v>
+        <v>46041</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6601,7 +6616,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.4</v>
+        <v>6.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6644,7 +6659,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6654,14 +6669,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45280</v>
+        <v>46077</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6674,7 +6689,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.7</v>
+        <v>0.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6717,7 +6732,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6727,14 +6742,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45016</v>
+        <v>46079</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6746,13 +6761,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6795,7 +6805,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6805,14 +6815,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45537</v>
+        <v>46079</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6824,13 +6834,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>6.6</v>
+        <v>3.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6873,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6883,14 +6888,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45007</v>
+        <v>46079</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6902,13 +6907,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6961,14 +6961,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44937</v>
+        <v>46079</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7034,14 +7034,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45593</v>
+        <v>46090</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>45253</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45244</v>
+        <v>44889</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1860,21 +1860,21 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>0.7</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1900,50 +1900,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1957,10 +1953,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45370</v>
+        <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1972,11 +1968,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2013,39 +2014,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
@@ -2069,7 +2066,7 @@
         <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2162,7 +2159,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2172,14 +2169,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44889</v>
+        <v>46077</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2191,13 +2188,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2206,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2224,7 +2216,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2237,35 +2229,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
@@ -2289,7 +2281,7 @@
         <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2369,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2383,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45979</v>
+        <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,16 +2398,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2452,42 +2439,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2497,14 +2488,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46077</v>
+        <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,11 +2507,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -2529,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2541,10 +2537,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2553,39 +2549,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44505</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>44599</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3206,14 +3206,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3227,11 +3227,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44916</v>
+        <v>45007</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,11 +3305,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3352,7 +3352,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3366,10 +3366,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45379</v>
+        <v>44599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45373</v>
+        <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3508,14 +3508,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45537</v>
+        <v>45379</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3527,13 +3527,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3576,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3586,14 +3581,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45537</v>
+        <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3605,13 +3600,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3654,7 +3644,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3668,10 +3658,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44937</v>
+        <v>45019</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3683,8 +3673,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>7.1</v>
+        <v>0.5</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3727,7 +3722,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3741,10 +3736,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44599</v>
+        <v>44680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3756,13 +3751,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3805,7 +3795,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3819,10 +3809,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44916</v>
+        <v>45835</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3834,13 +3824,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3883,7 +3868,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3897,10 +3882,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45553</v>
+        <v>45832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3913,7 +3898,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3956,7 +3941,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3970,10 +3955,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45007</v>
+        <v>45933</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3985,13 +3970,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4034,7 +4014,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4044,14 +4024,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45027</v>
+        <v>45537</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4065,11 +4045,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4112,7 +4092,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4122,14 +4102,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45344</v>
+        <v>45537</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4141,8 +4121,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4185,7 +4170,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4199,10 +4184,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45835</v>
+        <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4212,6 +4197,11 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>TROSA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -4258,7 +4248,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4272,10 +4262,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45832</v>
+        <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4287,8 +4277,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4331,7 +4326,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4341,14 +4336,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45736</v>
+        <v>46079</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4361,7 +4356,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>5.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4404,7 +4399,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4418,10 +4413,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44599</v>
+        <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4433,8 +4428,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4477,7 +4477,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46139</v>
+        <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4506,8 +4506,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4550,7 +4555,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4564,10 +4569,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44840</v>
+        <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4579,8 +4584,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4623,7 +4633,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4637,10 +4647,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45280</v>
+        <v>45988</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4652,8 +4662,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4696,7 +4711,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4710,10 +4725,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46079</v>
+        <v>45373</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4725,8 +4740,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>5.6</v>
+        <v>1.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4769,7 +4789,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4783,10 +4803,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45933</v>
+        <v>44756</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4799,7 +4819,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4842,7 +4862,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4856,10 +4876,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44840</v>
+        <v>45527</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4872,7 +4892,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.8</v>
+        <v>0.4</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4915,7 +4935,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4929,10 +4949,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44680</v>
+        <v>44916</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4944,8 +4964,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>7.7</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4988,7 +5013,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5002,10 +5027,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45016</v>
+        <v>46041</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5017,13 +5042,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I52" t="n">
-        <v>0.6</v>
+        <v>6.3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5066,7 +5086,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5076,14 +5096,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45537</v>
+        <v>46041</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5095,13 +5115,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I53" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5144,7 +5159,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5161,7 +5176,7 @@
         <v>45007</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5179,7 +5194,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5222,7 +5237,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5232,14 +5247,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45373</v>
+        <v>46077</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5251,13 +5266,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5300,7 +5310,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5314,10 +5324,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45373</v>
+        <v>46079</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5329,13 +5339,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I56" t="n">
-        <v>8.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5378,7 +5383,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5388,14 +5393,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44937</v>
+        <v>46079</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5408,7 +5413,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5451,7 +5456,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5461,14 +5466,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46273</v>
+        <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5481,7 +5486,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5524,7 +5529,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5534,14 +5539,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45019</v>
+        <v>46079</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5553,13 +5558,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I59" t="n">
-        <v>0.5</v>
+        <v>5.2</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5602,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>45968</v>
+        <v>46090</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5631,13 +5631,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5680,7 +5675,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5690,14 +5685,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45537</v>
+        <v>44599</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5711,11 +5706,11 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5758,7 +5753,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5772,10 +5767,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45968</v>
+        <v>44916</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5789,11 +5784,11 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5836,7 +5831,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5850,10 +5845,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45370</v>
+        <v>45553</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5866,7 +5861,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5909,7 +5904,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5923,10 +5918,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44756</v>
+        <v>44937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5939,7 +5934,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4.8</v>
+        <v>7.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5982,7 +5977,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5996,10 +5991,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45979</v>
+        <v>45344</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6011,13 +6006,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I65" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6060,7 +6050,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6074,10 +6064,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45979</v>
+        <v>45370</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6089,13 +6079,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.5</v>
+        <v>9.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6138,7 +6123,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6152,10 +6137,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45979</v>
+        <v>45027</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6169,11 +6154,11 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6216,7 +6201,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6230,10 +6215,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45527</v>
+        <v>45373</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6245,8 +6230,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6289,7 +6279,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6303,10 +6293,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45988</v>
+        <v>45373</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6318,13 +6308,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6367,7 +6352,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6377,14 +6362,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45593</v>
+        <v>46139</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6397,7 +6382,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6440,7 +6425,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6454,10 +6439,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45527</v>
+        <v>46273</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6470,7 +6455,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6513,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6523,14 +6508,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46041</v>
+        <v>45736</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6543,7 +6528,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6586,7 +6571,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6600,10 +6585,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46041</v>
+        <v>45280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6616,7 +6601,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6.3</v>
+        <v>2.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6659,7 +6644,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6669,14 +6654,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46077</v>
+        <v>45016</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6688,8 +6673,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6732,7 +6722,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6746,10 +6736,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46079</v>
+        <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6761,8 +6751,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6805,7 +6800,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6819,10 +6814,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46079</v>
+        <v>45007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6834,8 +6829,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>3.9</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6888,14 +6888,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46079</v>
+        <v>44937</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5.3</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6951,7 +6951,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>46079</v>
+        <v>45593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7024,7 +7024,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46090</v>
+        <v>45527</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5.1</v>
+        <v>1.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7114,7 +7114,7 @@
         <v>45253</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44889</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>46077</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44505</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>44599</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45537</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45007</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45379</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45019</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45835</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45933</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>45537</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45537</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>46079</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45988</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45373</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>44756</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45527</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>44916</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>46041</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>46041</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45007</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>46077</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>46079</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>46079</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>46079</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>46090</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44599</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>44916</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45553</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45344</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>45370</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45027</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45373</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45373</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>46139</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>46273</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>45736</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45016</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>44937</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>45593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45527</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45253</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         <v>44889</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>46077</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44505</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>44599</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         <v>45537</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45007</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>44599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45379</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44840</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45019</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>44680</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>45835</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45832</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45933</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>45537</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45537</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>46079</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45979</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45988</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4728,7 +4728,7 @@
         <v>45373</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>44756</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>45527</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>44916</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>46041</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>46041</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45007</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>46077</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>46079</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>46079</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>46079</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5619,7 +5619,7 @@
         <v>46090</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44599</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
         <v>44916</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>45553</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44937</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>45344</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>45370</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45027</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>45373</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>45373</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>46139</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>46273</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>45736</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45280</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45016</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
         <v>45007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>44937</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>45593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45527</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45253</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44889</v>
+        <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,16 +1858,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1904,42 +1899,46 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1949,14 +1948,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45979</v>
+        <v>44986</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1970,20 +1969,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1998,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2010,46 +2009,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2059,14 +2058,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44986</v>
+        <v>45244</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2080,11 +2079,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9.4</v>
+        <v>0.7</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2124,42 +2123,46 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2169,14 +2172,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46077</v>
+        <v>45979</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2188,8 +2191,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2198,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2216,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2229,42 +2237,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2274,14 +2282,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46220</v>
+        <v>46077</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2294,7 +2302,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>8.6</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2303,10 +2311,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2321,7 +2329,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2334,42 +2342,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2383,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45370</v>
+        <v>44889</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2398,11 +2406,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2439,46 +2452,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2492,10 +2501,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45244</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2507,23 +2516,18 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2537,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2549,43 +2553,39 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
         <v>44489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44505</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
         <v>44582</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>44599</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3213,7 +3213,7 @@
         <v>45537</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3284,14 +3284,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,11 +3305,11 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3352,7 +3352,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3366,10 +3366,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44599</v>
+        <v>44937</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3439,10 +3439,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44840</v>
+        <v>44916</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3454,8 +3454,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3498,7 +3503,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3512,10 +3517,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45379</v>
+        <v>45007</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3527,8 +3532,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3571,7 +3581,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3585,10 +3595,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44840</v>
+        <v>44599</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3600,8 +3610,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3644,7 +3659,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3658,10 +3673,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45019</v>
+        <v>45027</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3679,7 +3694,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3722,7 +3737,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3736,10 +3751,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44680</v>
+        <v>45344</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3752,7 +3767,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3795,7 +3810,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3809,10 +3824,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45835</v>
+        <v>44599</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3825,7 +3840,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3868,7 +3883,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3882,10 +3897,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45832</v>
+        <v>46139</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3898,7 +3913,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3941,7 +3956,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3955,10 +3970,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45933</v>
+        <v>45007</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3970,8 +3985,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4014,7 +4034,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4024,14 +4044,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45537</v>
+        <v>45933</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4043,13 +4063,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4092,7 +4107,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4102,14 +4117,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45537</v>
+        <v>44916</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4127,7 +4142,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4170,7 +4185,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4187,7 +4202,7 @@
         <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4205,7 +4220,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4248,7 +4263,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4265,7 +4280,7 @@
         <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4283,7 +4298,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4326,7 +4341,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4340,10 +4355,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46079</v>
+        <v>45379</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4356,7 +4371,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4399,7 +4414,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4413,10 +4428,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45979</v>
+        <v>45373</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4428,13 +4443,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4477,7 +4487,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4494,7 +4504,7 @@
         <v>45979</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4512,7 +4522,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4555,7 +4565,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4572,7 +4582,7 @@
         <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4590,7 +4600,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4633,7 +4643,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4647,10 +4657,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45988</v>
+        <v>45979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4664,11 +4674,11 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4711,7 +4721,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4725,10 +4735,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45373</v>
+        <v>46079</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4740,13 +4750,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>1.6</v>
+        <v>5.6</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4789,7 +4794,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4803,10 +4808,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44756</v>
+        <v>45988</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4818,8 +4823,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4862,7 +4872,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4876,10 +4886,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45527</v>
+        <v>45553</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4892,7 +4902,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.4</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4935,7 +4945,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4949,10 +4959,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44916</v>
+        <v>46041</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4964,13 +4974,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5030,7 +5035,7 @@
         <v>46041</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5086,7 +5091,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5096,14 +5101,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46041</v>
+        <v>45736</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5116,7 +5121,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5159,7 +5164,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5169,14 +5174,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45007</v>
+        <v>46077</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5188,13 +5193,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5237,7 +5237,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>5.2</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5327,7 +5327,7 @@
         <v>46079</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5400,7 +5400,7 @@
         <v>46079</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1.7</v>
+        <v>5.3</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5473,7 +5473,7 @@
         <v>46079</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>5.3</v>
+        <v>1.7</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5539,14 +5539,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46079</v>
+        <v>44840</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5.2</v>
+        <v>0.9</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5619,7 +5619,7 @@
         <v>46090</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44599</v>
+        <v>45280</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5704,13 +5704,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5753,7 +5748,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5767,10 +5762,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44916</v>
+        <v>45835</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5782,13 +5777,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5831,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5845,10 +5835,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45553</v>
+        <v>45832</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5861,7 +5851,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5904,7 +5894,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5918,10 +5908,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44937</v>
+        <v>44840</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5934,7 +5924,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7.1</v>
+        <v>2.8</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5977,7 +5967,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5991,10 +5981,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45344</v>
+        <v>44680</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6007,7 +5997,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6050,7 +6040,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6064,10 +6054,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45370</v>
+        <v>46273</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6080,7 +6070,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>9.5</v>
+        <v>4.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6123,7 +6113,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6137,10 +6127,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45027</v>
+        <v>45016</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6158,7 +6148,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6201,7 +6191,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6211,14 +6201,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45373</v>
+        <v>45537</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6232,11 +6222,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6279,7 +6269,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6293,10 +6283,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45373</v>
+        <v>45007</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6308,8 +6298,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6352,7 +6347,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6366,10 +6361,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46139</v>
+        <v>45373</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6381,8 +6376,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I70" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6425,7 +6425,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6439,10 +6439,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46273</v>
+        <v>45373</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6454,8 +6454,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6498,7 +6503,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6508,14 +6513,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45736</v>
+        <v>44937</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6528,7 +6533,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6571,7 +6576,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6585,10 +6590,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45280</v>
+        <v>45019</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6600,8 +6605,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6644,7 +6654,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6654,14 +6664,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45016</v>
+        <v>45537</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6675,11 +6685,11 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6722,7 +6732,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6732,14 +6742,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45537</v>
+        <v>45370</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6751,13 +6761,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>6.6</v>
+        <v>9.5</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6800,7 +6805,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6814,10 +6819,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45007</v>
+        <v>44756</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6829,13 +6834,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6878,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6892,10 +6892,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44937</v>
+        <v>45527</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6968,7 +6968,7 @@
         <v>45593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>45527</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>45253</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45714</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE81"/>
+  <dimension ref="A1:AE80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45370</v>
+        <v>46077</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,19 +1859,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,46 +1899,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1948,14 +1944,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44986</v>
+        <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1969,21 +1965,21 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>9.4</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
@@ -1997,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2009,46 +2005,46 @@
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2062,10 +2058,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45244</v>
+        <v>44889</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,21 +2075,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>0.7</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2107,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2119,50 +2115,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2172,14 +2164,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45979</v>
+        <v>44986</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2193,20 +2185,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>9.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2221,7 +2213,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2233,46 +2225,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2282,14 +2274,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46077</v>
+        <v>46220</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2302,7 +2294,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6</v>
+        <v>8.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2311,10 +2303,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2329,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2342,42 +2334,42 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2383,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44889</v>
+        <v>45370</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,16 +2398,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2452,42 +2439,46 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE18">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2501,10 +2492,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>45244</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,17 +2507,22 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -2541,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2553,39 +2549,43 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE19">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
         <v>44490</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         <v>44721</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>44733</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58922-2021</t>
+          <t>A 63049-2021</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44489</v>
+        <v>44505</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 63049-2021</t>
+          <t>A 3134-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44505</v>
+        <v>44582</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,11 +2998,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3045,7 +3045,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 3134-2022</t>
+          <t>A 6109-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44582</v>
+        <v>44599</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3074,13 +3074,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3123,7 +3118,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 6109-2022</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3133,14 +3128,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44599</v>
+        <v>45537</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3152,8 +3147,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3196,7 +3196,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3206,14 +3206,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45537</v>
+        <v>45007</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3227,11 +3227,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3274,7 +3274,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3284,14 +3284,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45537</v>
+        <v>44599</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3303,13 +3303,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3352,7 +3347,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3366,10 +3361,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44937</v>
+        <v>45527</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3382,7 +3377,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3425,7 +3420,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3439,10 +3434,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44916</v>
+        <v>44840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3454,13 +3449,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3503,7 +3493,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3517,10 +3507,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45007</v>
+        <v>46041</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3532,13 +3522,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3581,7 +3566,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3595,10 +3580,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44599</v>
+        <v>46041</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3610,13 +3595,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>0.7</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3659,7 +3639,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3673,10 +3653,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45027</v>
+        <v>45933</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3688,13 +3668,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3737,7 +3712,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3747,14 +3722,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45344</v>
+        <v>46077</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3767,7 +3742,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3810,7 +3785,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3824,10 +3799,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44599</v>
+        <v>46079</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3840,7 +3815,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3883,7 +3858,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3893,14 +3868,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3913,7 +3888,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3956,7 +3931,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3966,14 +3941,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45007</v>
+        <v>46079</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3985,13 +3960,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>5.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4034,7 +4004,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4044,14 +4014,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45933</v>
+        <v>46079</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4064,7 +4034,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4107,7 +4077,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4121,10 +4091,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44916</v>
+        <v>46090</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4136,13 +4106,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>5.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4185,7 +4150,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4202,7 +4167,7 @@
         <v>45968</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4220,7 +4185,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4263,7 +4228,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4280,7 +4245,7 @@
         <v>45968</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4298,7 +4263,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4341,7 +4306,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4355,10 +4320,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45379</v>
+        <v>44840</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4371,7 +4336,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4414,7 +4379,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4428,10 +4393,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45373</v>
+        <v>45019</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4443,8 +4408,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.2</v>
+        <v>0.5</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4487,7 +4457,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4501,10 +4471,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45979</v>
+        <v>45379</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4516,13 +4486,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4565,7 +4530,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4582,7 +4547,7 @@
         <v>45979</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4600,7 +4565,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4643,7 +4608,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4660,7 +4625,7 @@
         <v>45979</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4678,7 +4643,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4721,7 +4686,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4735,10 +4700,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46079</v>
+        <v>44680</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4751,7 +4716,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4794,7 +4759,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4808,10 +4773,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45988</v>
+        <v>45979</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4825,11 +4790,11 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4872,7 +4837,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4886,10 +4851,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45553</v>
+        <v>46139</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4902,7 +4867,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>1.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4945,7 +4910,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4959,10 +4924,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46041</v>
+        <v>45988</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4974,8 +4939,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I51" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -5018,7 +4988,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5032,10 +5002,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46041</v>
+        <v>45835</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5048,7 +5018,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6.3</v>
+        <v>3.5</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5091,7 +5061,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5101,14 +5071,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45736</v>
+        <v>45832</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5121,7 +5091,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5164,7 +5134,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5178,10 +5148,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46077</v>
+        <v>45537</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5193,8 +5163,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I54" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5237,7 +5212,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5251,10 +5226,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46079</v>
+        <v>45537</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5266,8 +5241,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I55" t="n">
-        <v>5.2</v>
+        <v>0.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5310,7 +5290,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5327,7 +5307,7 @@
         <v>46079</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5340,7 +5320,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5383,7 +5363,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5393,14 +5373,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46079</v>
+        <v>45373</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5412,8 +5392,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5456,7 +5441,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5466,14 +5451,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46079</v>
+        <v>44756</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5486,7 +5471,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.7</v>
+        <v>4.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5529,7 +5514,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5543,10 +5528,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44840</v>
+        <v>45527</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5559,7 +5544,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5602,7 +5587,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5616,10 +5601,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46090</v>
+        <v>44916</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5631,8 +5616,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I60" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5675,7 +5665,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5689,10 +5679,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45280</v>
+        <v>45007</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5704,8 +5694,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5748,7 +5743,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5762,10 +5757,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45835</v>
+        <v>44599</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5777,8 +5772,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5835,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45832</v>
+        <v>44916</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,8 +5850,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5894,7 +5899,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5908,10 +5913,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44840</v>
+        <v>45553</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5924,7 +5929,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5967,7 +5972,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5981,10 +5986,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44680</v>
+        <v>44937</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5997,7 +6002,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6040,7 +6045,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6054,10 +6059,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46273</v>
+        <v>45344</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6070,7 +6075,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6113,7 +6118,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6127,10 +6132,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45016</v>
+        <v>45370</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6142,13 +6147,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I67" t="n">
-        <v>0.6</v>
+        <v>9.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6191,7 +6191,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6201,14 +6201,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45537</v>
+        <v>45027</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6222,11 +6222,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Holmen skog AB</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 11742-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6283,10 +6283,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45007</v>
+        <v>45373</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6300,11 +6300,11 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>2.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6364,7 +6364,7 @@
         <v>45373</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6376,13 +6376,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6425,7 +6420,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 11742-2024</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6435,14 +6430,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45373</v>
+        <v>45736</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6454,13 +6449,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6503,7 +6493,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6517,10 +6507,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44937</v>
+        <v>45280</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6533,7 +6523,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>2.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6576,7 +6566,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6590,10 +6580,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45019</v>
+        <v>45016</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6611,7 +6601,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6654,7 +6644,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6664,14 +6654,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45537</v>
+        <v>46273</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6683,13 +6673,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6732,7 +6717,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6742,14 +6727,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45370</v>
+        <v>45537</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6761,8 +6746,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>9.5</v>
+        <v>6.6</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6805,7 +6795,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6819,10 +6809,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44756</v>
+        <v>45007</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6834,8 +6824,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I76" t="n">
-        <v>4.8</v>
+        <v>0.5</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6878,7 +6873,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6892,10 +6887,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45527</v>
+        <v>44937</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6908,7 +6903,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6968,7 +6963,7 @@
         <v>45593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7024,24 +7019,24 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>S 4203-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45527</v>
+        <v>45253</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7054,7 +7049,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7094,10 +7089,10 @@
       </c>
       <c r="V79" s="2" t="inlineStr"/>
     </row>
-    <row r="80" ht="15" customHeight="1">
+    <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>S 4203-2023</t>
+          <t>S 632-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7107,14 +7102,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45253</v>
+        <v>45714</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7126,8 +7121,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>3.6</v>
+        <v>36.2</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7166,84 +7166,6 @@
         <v>0</v>
       </c>
       <c r="V80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>S 632-2025</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E81" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>TROSA</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>0</v>
-      </c>
-      <c r="S81" t="n">
-        <v>0</v>
-      </c>
-      <c r="T81" t="n">
-        <v>0</v>
-      </c>
-      <c r="U81" t="n">
-        <v>0</v>
-      </c>
-      <c r="V81" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE80"/>
+  <dimension ref="A1:AE79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46077</v>
+        <v>45370</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,19 +1859,19 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1886,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1899,35 +1899,39 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
@@ -1951,7 +1955,7 @@
         <v>45979</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2044,7 +2048,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2054,14 +2058,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44889</v>
+        <v>44986</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2075,20 +2079,20 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7</v>
+        <v>9.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2103,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2115,46 +2119,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2168,10 +2172,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44986</v>
+        <v>46077</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2183,26 +2187,21 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>9.4</v>
+        <v>0.6</v>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -2213,10 +2212,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2225,46 +2224,46 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2278,10 +2277,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46220</v>
+        <v>45244</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2293,17 +2292,22 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -2318,7 +2322,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -2330,46 +2334,50 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2383,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45370</v>
+        <v>44889</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2398,11 +2406,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -2439,46 +2452,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2492,10 +2501,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45244</v>
+        <v>46220</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2507,23 +2516,18 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
@@ -2537,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2549,50 +2553,46 @@
         <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 59266-2021</t>
+          <t>A 23609-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44490</v>
+        <v>44721</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2621,13 +2621,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2670,7 +2665,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 23609-2022</t>
+          <t>A 29943-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2680,14 +2675,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44721</v>
+        <v>44756</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2700,7 +2695,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>11.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2743,7 +2738,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 29943-2022</t>
+          <t>A 25851-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2753,14 +2748,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44756</v>
+        <v>44733</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2773,7 +2768,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>11.4</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2816,7 +2811,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 25851-2022</t>
+          <t>A 63049-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2830,10 +2825,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44733</v>
+        <v>44505</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2845,8 +2840,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2889,7 +2889,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 63049-2021</t>
+          <t>A 3134-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2903,10 +2903,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44505</v>
+        <v>44582</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2920,11 +2920,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2967,7 +2967,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 3134-2022</t>
+          <t>A 6109-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2981,10 +2981,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44582</v>
+        <v>44599</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2996,13 +2996,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -3045,7 +3040,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 6109-2022</t>
+          <t>A 35054-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3059,10 +3054,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44599</v>
+        <v>45527</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3075,7 +3070,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3118,7 +3113,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 36710-2024</t>
+          <t>A 36709-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3135,7 +3130,7 @@
         <v>45537</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3153,7 +3148,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3196,7 +3191,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13839-2023</t>
+          <t>A 36711-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3206,14 +3201,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45007</v>
+        <v>45537</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3227,11 +3222,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3274,7 +3269,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 6102-2022</t>
+          <t>A 1589-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3288,10 +3283,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44599</v>
+        <v>44937</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3304,7 +3299,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.7</v>
+        <v>7.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3347,7 +3342,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35054-2024</t>
+          <t>A 6124-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3361,10 +3356,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45527</v>
+        <v>44599</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3376,8 +3371,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 44720-2022</t>
+          <t>A 62474-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3434,10 +3434,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44840</v>
+        <v>44916</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3449,8 +3449,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3493,7 +3498,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 3337-2026</t>
+          <t>A 48314-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3507,10 +3512,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46041</v>
+        <v>45933</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3523,7 +3528,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6.3</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3566,7 +3571,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 3346-2026</t>
+          <t>A 13810-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3580,10 +3585,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46041</v>
+        <v>45007</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3595,8 +3600,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3639,7 +3649,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 48314-2025</t>
+          <t>A 16029-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3653,10 +3663,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45933</v>
+        <v>45027</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3668,8 +3678,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>4.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3712,7 +3727,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10393-2026</t>
+          <t>A 7204-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3722,14 +3737,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46077</v>
+        <v>45344</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3742,7 +3757,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3785,7 +3800,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 11119-2026</t>
+          <t>A 55257-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3799,10 +3814,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46079</v>
+        <v>45968</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3814,8 +3829,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3858,7 +3878,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 11083-2026</t>
+          <t>A 55265-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3868,14 +3888,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46079</v>
+        <v>45968</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3887,8 +3907,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3931,7 +3956,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 11039-2026</t>
+          <t>A 3346-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3941,14 +3966,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46079</v>
+        <v>46041</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3961,7 +3986,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -4004,7 +4029,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 11069-2026</t>
+          <t>A 3337-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4014,14 +4039,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46079</v>
+        <v>46041</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4034,7 +4059,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.2</v>
+        <v>6.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -4077,7 +4102,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12574-2026</t>
+          <t>A 57342-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4091,10 +4116,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46090</v>
+        <v>45979</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4106,8 +4131,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>5.1</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -4150,7 +4180,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 55265-2025</t>
+          <t>A 57338-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4164,10 +4194,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45968</v>
+        <v>45979</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4181,11 +4211,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -4228,7 +4258,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 55257-2025</t>
+          <t>A 57344-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4242,10 +4272,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45968</v>
+        <v>45979</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4259,11 +4289,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -4306,7 +4336,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 44579-2022</t>
+          <t>A 6102-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4320,10 +4350,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44840</v>
+        <v>44599</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4336,7 +4366,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -4379,7 +4409,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 15293-2023</t>
+          <t>A 59222-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4393,10 +4423,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45019</v>
+        <v>45988</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4414,7 +4444,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4457,7 +4487,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 12447-2024</t>
+          <t>A 10393-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4467,14 +4497,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45379</v>
+        <v>46077</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4487,7 +4517,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4530,7 +4560,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 57342-2025</t>
+          <t>A 11069-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4540,14 +4570,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45979</v>
+        <v>46079</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4559,13 +4589,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -4608,7 +4633,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 57338-2025</t>
+          <t>A 11119-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4622,10 +4647,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45979</v>
+        <v>46079</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4637,13 +4662,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -4686,7 +4706,7 @@
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 17600-2022</t>
+          <t>A 11039-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4696,14 +4716,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>44680</v>
+        <v>46079</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -4716,7 +4736,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7.7</v>
+        <v>5.3</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -4759,7 +4779,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 57344-2025</t>
+          <t>A 11083-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4769,14 +4789,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45979</v>
+        <v>46079</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -4788,13 +4808,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -4837,7 +4852,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 20191-2026</t>
+          <t>A 13829-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4851,10 +4866,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46139</v>
+        <v>45007</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -4866,8 +4881,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
@@ -4910,7 +4930,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 59222-2025</t>
+          <t>A 12574-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4924,10 +4944,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45988</v>
+        <v>46090</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4939,13 +4959,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>0.6</v>
+        <v>5.1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -4988,7 +5003,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 32213-2025</t>
+          <t>A 62473-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5002,10 +5017,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45835</v>
+        <v>44916</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5017,8 +5032,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I52" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -5061,7 +5081,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 31166-2025</t>
+          <t>A 12447-2024</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5075,10 +5095,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45832</v>
+        <v>45379</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5091,7 +5111,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -5134,7 +5154,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 36709-2024</t>
+          <t>A 11743-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5144,14 +5164,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45537</v>
+        <v>45373</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5163,13 +5183,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -5212,7 +5227,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 36711-2024</t>
+          <t>A 32213-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5222,14 +5237,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45537</v>
+        <v>45835</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5241,13 +5256,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I55" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -5290,7 +5300,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 11103-2026</t>
+          <t>A 31166-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5304,10 +5314,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46079</v>
+        <v>45832</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5320,7 +5330,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -5363,7 +5373,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 11740-2024</t>
+          <t>A 39827-2024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5377,10 +5387,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45373</v>
+        <v>45553</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5392,13 +5402,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I57" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -5441,7 +5446,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 29930-2022</t>
+          <t>A 20191-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5455,10 +5460,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44756</v>
+        <v>46139</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5471,7 +5476,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4.8</v>
+        <v>1.2</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -5514,7 +5519,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 35058-2024</t>
+          <t>A 13675-2025</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5524,14 +5529,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>45527</v>
+        <v>45736</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5544,7 +5549,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -5587,7 +5592,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 62474-2022</t>
+          <t>A 11103-2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5601,10 +5606,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44916</v>
+        <v>46079</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5616,13 +5621,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I60" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -5665,7 +5665,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 13810-2023</t>
+          <t>A 44720-2022</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>45007</v>
+        <v>44840</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -5694,13 +5694,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I61" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -5743,7 +5738,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 6124-2022</t>
+          <t>A 64286-2023</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5757,10 +5752,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44599</v>
+        <v>45280</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -5772,13 +5767,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -5821,7 +5811,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 62473-2022</t>
+          <t>A 44579-2022</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5835,10 +5825,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44916</v>
+        <v>44840</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -5850,13 +5840,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -5899,7 +5884,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 39827-2024</t>
+          <t>A 17600-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5913,10 +5898,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45553</v>
+        <v>44680</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5929,7 +5914,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>5</v>
+        <v>7.7</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -5972,7 +5957,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 1589-2023</t>
+          <t>A 15169-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5986,10 +5971,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44937</v>
+        <v>45016</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6001,8 +5986,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I65" t="n">
-        <v>7.1</v>
+        <v>0.6</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6045,7 +6035,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7204-2024</t>
+          <t>A 36712-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6055,14 +6045,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45344</v>
+        <v>45537</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6074,8 +6064,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6118,7 +6113,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 10998-2024</t>
+          <t>A 13839-2023</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6132,10 +6127,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45370</v>
+        <v>45007</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6147,8 +6142,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I67" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6191,7 +6191,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 16029-2023</t>
+          <t>A 11740-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45027</v>
+        <v>45373</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6222,11 +6222,11 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Holmen skog AB</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6286,7 +6286,7 @@
         <v>45373</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6347,7 +6347,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 11743-2024</t>
+          <t>A 1431-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6361,10 +6361,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45373</v>
+        <v>44937</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6420,7 +6420,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13675-2025</t>
+          <t>A 15293-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6430,14 +6430,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45736</v>
+        <v>45019</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6449,8 +6449,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>1.4</v>
+        <v>0.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6493,7 +6498,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 64286-2023</t>
+          <t>A 36710-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6503,14 +6508,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45280</v>
+        <v>45537</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6522,8 +6527,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I72" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -6566,7 +6576,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 15169-2023</t>
+          <t>A 10998-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6580,10 +6590,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45016</v>
+        <v>45370</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6595,13 +6605,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>0.6</v>
+        <v>9.5</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -6644,7 +6649,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 36944-2026</t>
+          <t>A 29930-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6658,10 +6663,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46273</v>
+        <v>44756</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6674,7 +6679,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -6717,7 +6722,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 36712-2024</t>
+          <t>A 35058-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6727,14 +6732,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45537</v>
+        <v>45527</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6746,13 +6751,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I75" t="n">
-        <v>6.6</v>
+        <v>0.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 13829-2023</t>
+          <t>A 48793-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6805,14 +6805,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45007</v>
+        <v>45593</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6824,13 +6824,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6873,7 +6868,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 1431-2023</t>
+          <t>A 36944-2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6887,10 +6882,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44937</v>
+        <v>46273</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -6903,7 +6898,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -6946,24 +6941,24 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 48793-2024</t>
+          <t>S 4203-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45593</v>
+        <v>45253</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6976,7 +6971,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7016,10 +7011,10 @@
       </c>
       <c r="V78" s="2" t="inlineStr"/>
     </row>
-    <row r="79" ht="15" customHeight="1">
+    <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>S 4203-2023</t>
+          <t>S 632-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7029,14 +7024,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45253</v>
+        <v>45714</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7048,8 +7043,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>3.6</v>
+        <v>36.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7088,84 +7088,6 @@
         <v>0</v>
       </c>
       <c r="V79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>S 632-2025</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="n">
-        <v>45714</v>
-      </c>
-      <c r="E80" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>SÖDERMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>TROSA</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TROSA.xlsx
+++ b/Översikt TROSA.xlsx
@@ -601,7 +601,7 @@
         <v>45930</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>45614</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>45593</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         <v>44649</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45141</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44505</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44944</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>45275</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45373</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45603</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44533</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 11066-2024</t>
+          <t>A 11123-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1839,14 +1839,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45370</v>
+        <v>44986</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1858,8 +1858,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.3</v>
+        <v>9.4</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1868,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1883,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1895,50 +1900,46 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Nötkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
-        <v/>
-      </c>
-      <c r="AE13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 57251-2025</t>
+          <t>A 11066-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1952,10 +1953,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45979</v>
+        <v>45370</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1967,16 +1968,11 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -2013,42 +2009,46 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11066-2024 artfynd.xlsx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11066-2024 karta.png", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11066-2024 georefererad karta.tif", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11066-2024 FSC-klagomål.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11066-2024 FSC-klagomål mail.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11066-2024 tillsynsbegäran.docx", "A 11066-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11066-2024 tillsynsbegäran mail.docx", "A 11066-2024")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 11066-2024 prioriterade fågelarter.docx", "A 11066-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 11123-2023</t>
+          <t>A 57251-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2058,14 +2058,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44986</v>
+        <v>45979</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2079,21 +2079,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9.4</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
         <v>0</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2119,46 +2119,46 @@
         <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 11123-2023 artfynd.xlsx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57251-2025 artfynd.xlsx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 11123-2023 karta.png", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57251-2025 karta.png", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 11123-2023 georefererad karta.tif", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57251-2025 georefererad karta.tif", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 11123-2023 FSC-klagomål.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57251-2025 FSC-klagomål.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 11123-2023 FSC-klagomål mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57251-2025 FSC-klagomål mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 11123-2023 tillsynsbegäran.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57251-2025 tillsynsbegäran.docx", "A 57251-2025")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 11123-2023 tillsynsbegäran mail.docx", "A 11123-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57251-2025 tillsynsbegäran mail.docx", "A 57251-2025")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 10390-2026</t>
+          <t>A 57004-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2168,14 +2168,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46077</v>
+        <v>45244</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2187,11 +2187,16 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2200,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2212,10 +2217,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2224,46 +2229,50 @@
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
+        <v/>
+      </c>
+      <c r="AE16">
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 57004-2023</t>
+          <t>A 10390-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2273,14 +2282,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45244</v>
+        <v>46077</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2292,26 +2301,21 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -2322,10 +2326,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2334,50 +2338,46 @@
         <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 57004-2023 artfynd.xlsx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 10390-2026 artfynd.xlsx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="X17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 57004-2023 karta.png", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 10390-2026 karta.png", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="Y17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 57004-2023 georefererad karta.tif", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 10390-2026 georefererad karta.tif", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AA17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 57004-2023 FSC-klagomål.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 10390-2026 FSC-klagomål.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AB17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 57004-2023 FSC-klagomål mail.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 10390-2026 FSC-klagomål mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AC17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 57004-2023 tillsynsbegäran.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 10390-2026 tillsynsbegäran.docx", "A 10390-2026")</f>
         <v/>
       </c>
       <c r="AD17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 57004-2023 tillsynsbegäran mail.docx", "A 57004-2023")</f>
-        <v/>
-      </c>
-      <c r="AE17">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/fåglar/A 57004-2023 prioriterade fågelarter.docx", "A 57004-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 10390-2026 tillsynsbegäran mail.docx", "A 10390-2026")</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 56117-2022</t>
+          <t>A 31394-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44889</v>
+        <v>46220</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2406,13 +2406,8 @@
           <t>TROSA</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Holmen skog AB</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>8.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2452,42 +2447,42 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>Älg</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 56117-2022 tillsynsbegäran mail.docx", "A 56117-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsynsmail/A 31394-2026 tillsynsbegäran mail.docx", "A 31394-2026")</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 31394-2026</t>
+          <t>A 56117-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2501,10 +2496,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46220</v>
+        <v>44889</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2516,8 +2511,13 @@
           <t>TROSA</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Holmen skog AB</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2557,35 +2557,35 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="W19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 31394-2026 artfynd.xlsx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/artfynd/A 56117-2022 artfynd.xlsx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="X19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 31394-2026 karta.png", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor/A 56117-2022 karta.png", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="Y19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 31394-2026 georefererad karta.tif", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/kartor_geotiff/A 56117-2022 georefererad karta.tif", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AA19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 31394-2026 FSC-klagomål.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomål/A 56117-2022 FSC-klagomål.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AB19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 31394-2026 FSC-klagomål mail.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/klagomålsmail/A 56117-2022 FSC-klagomål mail.docx", "A 56117-2022")</f>
         <v/>
       </c>
       <c r="AC19">
-        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 31394-2026 tillsynsbegäran.docx", "A 31394-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_0488/tillsyn/A 56117-2022 tillsynsbegäran.